--- a/assets/BECM_2K22_3-2_Attendance_Tracker.xlsx
+++ b/assets/BECM_2K22_3-2_Attendance_Tracker.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R95176f0b8e004fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Log" sheetId="2" r:id="R41b38d62da264f4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routine &amp; Settings" sheetId="3" r:id="Reb314628939a4a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R45e61078583a4897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Log" sheetId="2" r:id="Rcc96a28dbc4e44a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routine &amp; Settings" sheetId="3" r:id="R6a1b278affb14743"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -101,8 +101,14 @@
       <x:color rgb="FF92400E"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -174,6 +180,11 @@
         <x:fgColor rgb="FFF0FDFA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F1FF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -182,7 +193,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="207">
+  <x:cellXfs count="221">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -650,6 +661,40 @@
     <x:xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="14" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -661,7 +706,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -672,7 +717,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -683,7 +728,7 @@
         <x:color rgb="FF64748B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF1F5F9"/>
         </x:patternFill>
       </x:fill>
@@ -694,7 +739,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -705,7 +750,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -716,7 +761,7 @@
         <x:color rgb="FF64748B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF1F5F9"/>
         </x:patternFill>
       </x:fill>
@@ -726,7 +771,7 @@
         <x:color rgb="FF94A3B8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8FAFC"/>
         </x:patternFill>
       </x:fill>
@@ -737,7 +782,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -748,7 +793,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -759,7 +804,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -789,6 +834,7 @@
     <c:plotArea>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -908,7 +954,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R27532231392643bb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61b0de2be8d54adf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1152,7 +1198,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>60% minimum attendance for exam eligibility • 13 teaching weeks • Puja break excluded • Update only the Attendance dropdown in Class Log</x:v>
+        <x:v>60% minimum attendance for exam eligibility • 13 teaching weeks • Routine revised from Week 4 (Sunday, 27 Sep 2026) • Update only the Attendance dropdown in Class Log</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -1607,7 +1653,7 @@
       </x:c>
       <x:c r="C19" s="23" t="n">
         <x:f>COUNTIFS('Class Log'!$E$5:$E$290,"BECM 3208",'Class Log'!$P$5:$P$290,"Yes")</x:f>
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D19" s="23" t="n">
         <x:f>COUNTIFS('Class Log'!$E$5:$E$400,"BECM 3208",'Class Log'!$P$5:$P$400,"Yes",'Class Log'!$K$5:$K$400,"Attended")+COUNTIFS('Class Log'!$E$5:$E$400,"BECM 3208",'Class Log'!$P$5:$P$400,"Yes",'Class Log'!$K$5:$K$400,"Missed")</x:f>
@@ -1648,7 +1694,7 @@
       </x:c>
       <x:c r="C20" s="23" t="n">
         <x:f>COUNTIFS('Class Log'!$E$5:$E$290,"CE 3224",'Class Log'!$P$5:$P$290,"Yes")</x:f>
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
         <x:f>COUNTIFS('Class Log'!$E$5:$E$400,"CE 3224",'Class Log'!$P$5:$P$400,"Yes",'Class Log'!$K$5:$K$400,"Attended")+COUNTIFS('Class Log'!$E$5:$E$400,"CE 3224",'Class Log'!$P$5:$P$400,"Yes",'Class Log'!$K$5:$K$400,"Missed")</x:f>
@@ -1891,6 +1937,7 @@
     <x:mergeCell ref="A22:J23"/>
     <x:mergeCell ref="A25:P25"/>
     <x:mergeCell ref="A42:P42"/>
+    <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="H12:H20">
     <x:cfRule type="colorScale" priority="1">
@@ -1927,7 +1974,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8bc6bbd5a94e25"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R375db2ec50d94a70"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1991,7 +2038,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Daily use: choose Attended / Missed / Cancelled. Blank = not marked yet. Cancelled classes never reduce attendance.</x:v>
+        <x:v>Daily use: choose Attended / Missed / Cancelled. Blank = not marked yet. Cancelled classes never reduce attendance. Revised routine applies from Sunday, 27 Sep 2026 (Week 4).</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -2421,7 +2468,7 @@
       <x:c r="O13" s="173" t="str"/>
       <x:c r="P13" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A13)&gt;0,"No",IF(E13="BECM 3204",IF(J13='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E13="BECM 3208",IF(J13='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E13="CE 3224",IF(J13='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E13="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C13,2)=1,"Yes","No"),IF(MOD(C13,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2542,7 +2589,7 @@
       <x:c r="O16" s="173" t="str"/>
       <x:c r="P16" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A16)&gt;0,"No",IF(E16="BECM 3204",IF(J16='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E16="BECM 3208",IF(J16='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E16="CE 3224",IF(J16='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E16="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C16,2)=1,"Yes","No"),IF(MOD(C16,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3315,7 +3362,7 @@
       <x:c r="O35" s="173" t="str"/>
       <x:c r="P35" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A35)&gt;0,"No",IF(E35="BECM 3204",IF(J35='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E35="BECM 3208",IF(J35='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E35="CE 3224",IF(J35='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E35="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C35,2)=1,"Yes","No"),IF(MOD(C35,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3436,7 +3483,7 @@
       <x:c r="O38" s="173" t="str"/>
       <x:c r="P38" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A38)&gt;0,"No",IF(E38="BECM 3204",IF(J38='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E38="BECM 3208",IF(J38='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E38="CE 3224",IF(J38='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E38="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C38,2)=1,"Yes","No"),IF(MOD(C38,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4209,7 +4256,7 @@
       <x:c r="O57" s="173" t="str"/>
       <x:c r="P57" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A57)&gt;0,"No",IF(E57="BECM 3204",IF(J57='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E57="BECM 3208",IF(J57='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E57="CE 3224",IF(J57='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E57="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C57,2)=1,"Yes","No"),IF(MOD(C57,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -4330,7 +4377,7 @@
       <x:c r="O60" s="173" t="str"/>
       <x:c r="P60" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A60)&gt;0,"No",IF(E60="BECM 3204",IF(J60='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E60="BECM 3208",IF(J60='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E60="CE 3224",IF(J60='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E60="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C60,2)=1,"Yes","No"),IF(MOD(C60,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -4767,16 +4814,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I71" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J71" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K71" s="131" t="str"/>
-      <x:c r="L71" s="143" t="str"/>
-      <x:c r="M71" s="143" t="str"/>
-      <x:c r="N71" s="143" t="str"/>
-      <x:c r="O71" s="173" t="str"/>
+      <x:c r="K71" s="131"/>
+      <x:c r="L71" s="143"/>
+      <x:c r="M71" s="143"/>
+      <x:c r="N71" s="143"/>
+      <x:c r="O71" s="173"/>
       <x:c r="P71" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A71)&gt;0,"No",IF(E71="BECM 3204",IF(J71='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E71="BECM 3208",IF(J71='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E71="CE 3224",IF(J71='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E71="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C71,2)=1,"Yes","No"),IF(MOD(C71,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -4796,28 +4843,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E72" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F72" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G72" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H72" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I72" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J72" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K72" s="131" t="str"/>
-      <x:c r="L72" s="143" t="str"/>
-      <x:c r="M72" s="143" t="str"/>
-      <x:c r="N72" s="143" t="str"/>
-      <x:c r="O72" s="173" t="str"/>
+      <x:c r="K72" s="131"/>
+      <x:c r="L72" s="143"/>
+      <x:c r="M72" s="143"/>
+      <x:c r="N72" s="143"/>
+      <x:c r="O72" s="173"/>
       <x:c r="P72" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A72)&gt;0,"No",IF(E72="BECM 3204",IF(J72='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E72="BECM 3208",IF(J72='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E72="CE 3224",IF(J72='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E72="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C72,2)=1,"Yes","No"),IF(MOD(C72,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -4837,28 +4884,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E73" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F73" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G73" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H73" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I73" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J73" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K73" s="131" t="str"/>
-      <x:c r="L73" s="143" t="str"/>
-      <x:c r="M73" s="143" t="str"/>
-      <x:c r="N73" s="143" t="str"/>
-      <x:c r="O73" s="173" t="str"/>
+      <x:c r="K73" s="131"/>
+      <x:c r="L73" s="143"/>
+      <x:c r="M73" s="143"/>
+      <x:c r="N73" s="143"/>
+      <x:c r="O73" s="173"/>
       <x:c r="P73" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A73)&gt;0,"No",IF(E73="BECM 3204",IF(J73='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E73="BECM 3208",IF(J73='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E73="CE 3224",IF(J73='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E73="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C73,2)=1,"Yes","No"),IF(MOD(C73,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -4889,17 +4936,15 @@
       <x:c r="H74" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I74" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I74" s="23"/>
       <x:c r="J74" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K74" s="131" t="str"/>
-      <x:c r="L74" s="143" t="str"/>
-      <x:c r="M74" s="143" t="str"/>
-      <x:c r="N74" s="143" t="str"/>
-      <x:c r="O74" s="173" t="str"/>
+      <x:c r="K74" s="131"/>
+      <x:c r="L74" s="143"/>
+      <x:c r="M74" s="143"/>
+      <x:c r="N74" s="143"/>
+      <x:c r="O74" s="173"/>
       <x:c r="P74" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A74)&gt;0,"No",IF(E74="BECM 3204",IF(J74='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E74="BECM 3208",IF(J74='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E74="CE 3224",IF(J74='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E74="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C74,2)=1,"Yes","No"),IF(MOD(C74,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -4919,28 +4964,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E75" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F75" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G75" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H75" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I75" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J75" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K75" s="131" t="str"/>
-      <x:c r="L75" s="143" t="str"/>
-      <x:c r="M75" s="143" t="str"/>
-      <x:c r="N75" s="143" t="str"/>
-      <x:c r="O75" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K75" s="131"/>
+      <x:c r="L75" s="143"/>
+      <x:c r="M75" s="143"/>
+      <x:c r="N75" s="143"/>
+      <x:c r="O75" s="173"/>
       <x:c r="P75" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A75)&gt;0,"No",IF(E75="BECM 3204",IF(J75='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E75="BECM 3208",IF(J75='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E75="CE 3224",IF(J75='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E75="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C75,2)=1,"Yes","No"),IF(MOD(C75,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -4972,16 +5017,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I76" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J76" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K76" s="131" t="str"/>
-      <x:c r="L76" s="143" t="str"/>
-      <x:c r="M76" s="143" t="str"/>
-      <x:c r="N76" s="143" t="str"/>
-      <x:c r="O76" s="173" t="str"/>
+      <x:c r="K76" s="131"/>
+      <x:c r="L76" s="143"/>
+      <x:c r="M76" s="143"/>
+      <x:c r="N76" s="143"/>
+      <x:c r="O76" s="173"/>
       <x:c r="P76" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A76)&gt;0,"No",IF(E76="BECM 3204",IF(J76='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E76="BECM 3208",IF(J76='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E76="CE 3224",IF(J76='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E76="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C76,2)=1,"Yes","No"),IF(MOD(C76,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5013,16 +5058,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I77" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J77" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K77" s="131" t="str"/>
-      <x:c r="L77" s="143" t="str"/>
-      <x:c r="M77" s="143" t="str"/>
-      <x:c r="N77" s="143" t="str"/>
-      <x:c r="O77" s="173" t="str"/>
+      <x:c r="K77" s="131"/>
+      <x:c r="L77" s="143"/>
+      <x:c r="M77" s="143"/>
+      <x:c r="N77" s="143"/>
+      <x:c r="O77" s="173"/>
       <x:c r="P77" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A77)&gt;0,"No",IF(E77="BECM 3204",IF(J77='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E77="BECM 3208",IF(J77='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E77="CE 3224",IF(J77='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E77="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C77,2)=1,"Yes","No"),IF(MOD(C77,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5042,29 +5087,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E78" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F78" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G78" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H78" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I78" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I78" s="23"/>
       <x:c r="J78" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K78" s="131" t="str"/>
-      <x:c r="L78" s="143" t="str"/>
-      <x:c r="M78" s="143" t="str"/>
-      <x:c r="N78" s="143" t="str"/>
-      <x:c r="O78" s="173" t="str"/>
+      <x:c r="K78" s="131"/>
+      <x:c r="L78" s="143"/>
+      <x:c r="M78" s="143"/>
+      <x:c r="N78" s="143"/>
+      <x:c r="O78" s="173"/>
       <x:c r="P78" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A78)&gt;0,"No",IF(E78="BECM 3204",IF(J78='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E78="BECM 3208",IF(J78='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E78="CE 3224",IF(J78='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E78="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C78,2)=1,"Yes","No"),IF(MOD(C78,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -5081,26 +5126,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E79" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F79" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G79" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H79" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I79" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I79" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J79" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K79" s="131" t="str"/>
-      <x:c r="L79" s="143" t="str"/>
-      <x:c r="M79" s="143" t="str"/>
-      <x:c r="N79" s="143" t="str"/>
-      <x:c r="O79" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K79" s="131"/>
+      <x:c r="L79" s="143"/>
+      <x:c r="M79" s="143"/>
+      <x:c r="N79" s="143"/>
+      <x:c r="O79" s="173"/>
       <x:c r="P79" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A79)&gt;0,"No",IF(E79="BECM 3204",IF(J79='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E79="BECM 3208",IF(J79='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E79="CE 3224",IF(J79='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E79="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C79,2)=1,"Yes","No"),IF(MOD(C79,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5120,28 +5167,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E80" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F80" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G80" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H80" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I80" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J80" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K80" s="131" t="str"/>
-      <x:c r="L80" s="143" t="str"/>
-      <x:c r="M80" s="143" t="str"/>
-      <x:c r="N80" s="143" t="str"/>
-      <x:c r="O80" s="173" t="str"/>
+      <x:c r="K80" s="131"/>
+      <x:c r="L80" s="143"/>
+      <x:c r="M80" s="143"/>
+      <x:c r="N80" s="143"/>
+      <x:c r="O80" s="173"/>
       <x:c r="P80" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A80)&gt;0,"No",IF(E80="BECM 3204",IF(J80='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E80="BECM 3208",IF(J80='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E80="CE 3224",IF(J80='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E80="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C80,2)=1,"Yes","No"),IF(MOD(C80,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5161,28 +5208,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E81" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F81" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G81" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H81" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I81" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J81" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K81" s="131" t="str"/>
-      <x:c r="L81" s="143" t="str"/>
-      <x:c r="M81" s="143" t="str"/>
-      <x:c r="N81" s="143" t="str"/>
-      <x:c r="O81" s="173" t="str"/>
+      <x:c r="K81" s="131"/>
+      <x:c r="L81" s="143"/>
+      <x:c r="M81" s="143"/>
+      <x:c r="N81" s="143"/>
+      <x:c r="O81" s="173"/>
       <x:c r="P81" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A81)&gt;0,"No",IF(E81="BECM 3204",IF(J81='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E81="BECM 3208",IF(J81='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E81="CE 3224",IF(J81='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E81="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C81,2)=1,"Yes","No"),IF(MOD(C81,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5202,26 +5249,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E82" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F82" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G82" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H82" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I82" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I82" s="23"/>
       <x:c r="J82" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K82" s="131" t="str"/>
-      <x:c r="L82" s="143" t="str"/>
-      <x:c r="M82" s="143" t="str"/>
-      <x:c r="N82" s="143" t="str"/>
-      <x:c r="O82" s="173" t="str"/>
+      <x:c r="K82" s="131"/>
+      <x:c r="L82" s="143"/>
+      <x:c r="M82" s="143"/>
+      <x:c r="N82" s="143"/>
+      <x:c r="O82" s="173"/>
       <x:c r="P82" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A82)&gt;0,"No",IF(E82="BECM 3204",IF(J82='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E82="BECM 3208",IF(J82='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E82="CE 3224",IF(J82='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E82="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C82,2)=1,"Yes","No"),IF(MOD(C82,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5241,31 +5288,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E83" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F83" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G83" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H83" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I83" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I83" s="23"/>
       <x:c r="J83" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K83" s="131" t="str"/>
-      <x:c r="L83" s="143" t="str"/>
-      <x:c r="M83" s="143" t="str"/>
-      <x:c r="N83" s="143" t="str"/>
-      <x:c r="O83" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K83" s="131"/>
+      <x:c r="L83" s="143"/>
+      <x:c r="M83" s="143"/>
+      <x:c r="N83" s="143"/>
+      <x:c r="O83" s="173"/>
       <x:c r="P83" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A83)&gt;0,"No",IF(E83="BECM 3204",IF(J83='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E83="BECM 3208",IF(J83='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E83="CE 3224",IF(J83='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E83="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C83,2)=1,"Yes","No"),IF(MOD(C83,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -5282,28 +5327,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E84" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F84" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G84" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H84" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I84" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J84" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K84" s="131" t="str"/>
-      <x:c r="L84" s="143" t="str"/>
-      <x:c r="M84" s="143" t="str"/>
-      <x:c r="N84" s="143" t="str"/>
-      <x:c r="O84" s="173" t="str"/>
+      <x:c r="K84" s="131"/>
+      <x:c r="L84" s="143"/>
+      <x:c r="M84" s="143"/>
+      <x:c r="N84" s="143"/>
+      <x:c r="O84" s="173"/>
       <x:c r="P84" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A84)&gt;0,"No",IF(E84="BECM 3204",IF(J84='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E84="BECM 3208",IF(J84='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E84="CE 3224",IF(J84='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E84="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C84,2)=1,"Yes","No"),IF(MOD(C84,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5323,28 +5368,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E85" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F85" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G85" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H85" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I85" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J85" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K85" s="131" t="str"/>
-      <x:c r="L85" s="143" t="str"/>
-      <x:c r="M85" s="143" t="str"/>
-      <x:c r="N85" s="143" t="str"/>
-      <x:c r="O85" s="173" t="str"/>
+      <x:c r="K85" s="131"/>
+      <x:c r="L85" s="143"/>
+      <x:c r="M85" s="143"/>
+      <x:c r="N85" s="143"/>
+      <x:c r="O85" s="173"/>
       <x:c r="P85" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A85)&gt;0,"No",IF(E85="BECM 3204",IF(J85='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E85="BECM 3208",IF(J85='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E85="CE 3224",IF(J85='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E85="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C85,2)=1,"Yes","No"),IF(MOD(C85,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5376,16 +5421,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I86" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J86" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K86" s="131" t="str"/>
-      <x:c r="L86" s="143" t="str"/>
-      <x:c r="M86" s="143" t="str"/>
-      <x:c r="N86" s="143" t="str"/>
-      <x:c r="O86" s="173" t="str"/>
+      <x:c r="K86" s="131"/>
+      <x:c r="L86" s="143"/>
+      <x:c r="M86" s="143"/>
+      <x:c r="N86" s="143"/>
+      <x:c r="O86" s="173"/>
       <x:c r="P86" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A86)&gt;0,"No",IF(E86="BECM 3204",IF(J86='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E86="BECM 3208",IF(J86='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E86="CE 3224",IF(J86='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E86="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C86,2)=1,"Yes","No"),IF(MOD(C86,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5405,28 +5450,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E87" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F87" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G87" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H87" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I87" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I87" s="23"/>
       <x:c r="J87" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K87" s="131" t="str"/>
-      <x:c r="L87" s="143" t="str"/>
-      <x:c r="M87" s="143" t="str"/>
-      <x:c r="N87" s="143" t="str"/>
-      <x:c r="O87" s="173" t="str"/>
+      <x:c r="K87" s="131"/>
+      <x:c r="L87" s="143"/>
+      <x:c r="M87" s="143"/>
+      <x:c r="N87" s="143"/>
+      <x:c r="O87" s="173"/>
       <x:c r="P87" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A87)&gt;0,"No",IF(E87="BECM 3204",IF(J87='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E87="BECM 3208",IF(J87='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E87="CE 3224",IF(J87='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E87="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C87,2)=1,"Yes","No"),IF(MOD(C87,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -5446,26 +5489,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E88" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F88" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G88" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H88" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I88" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I88" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J88" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K88" s="131" t="str"/>
-      <x:c r="L88" s="143" t="str"/>
-      <x:c r="M88" s="143" t="str"/>
-      <x:c r="N88" s="143" t="str"/>
-      <x:c r="O88" s="173" t="str"/>
+      <x:c r="K88" s="131"/>
+      <x:c r="L88" s="143"/>
+      <x:c r="M88" s="143"/>
+      <x:c r="N88" s="143"/>
+      <x:c r="O88" s="173"/>
       <x:c r="P88" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A88)&gt;0,"No",IF(E88="BECM 3204",IF(J88='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E88="BECM 3208",IF(J88='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E88="CE 3224",IF(J88='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E88="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C88,2)=1,"Yes","No"),IF(MOD(C88,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -5485,28 +5530,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E89" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F89" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G89" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H89" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I89" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J89" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K89" s="131" t="str"/>
-      <x:c r="L89" s="143" t="str"/>
-      <x:c r="M89" s="143" t="str"/>
-      <x:c r="N89" s="143" t="str"/>
-      <x:c r="O89" s="173" t="str"/>
+      <x:c r="K89" s="131"/>
+      <x:c r="L89" s="143"/>
+      <x:c r="M89" s="143"/>
+      <x:c r="N89" s="143"/>
+      <x:c r="O89" s="173"/>
       <x:c r="P89" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A89)&gt;0,"No",IF(E89="BECM 3204",IF(J89='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E89="BECM 3208",IF(J89='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E89="CE 3224",IF(J89='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E89="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C89,2)=1,"Yes","No"),IF(MOD(C89,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5526,28 +5571,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E90" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F90" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G90" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H90" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I90" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J90" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K90" s="131" t="str"/>
-      <x:c r="L90" s="143" t="str"/>
-      <x:c r="M90" s="143" t="str"/>
-      <x:c r="N90" s="143" t="str"/>
-      <x:c r="O90" s="173" t="str"/>
+      <x:c r="K90" s="131"/>
+      <x:c r="L90" s="143"/>
+      <x:c r="M90" s="143"/>
+      <x:c r="N90" s="143"/>
+      <x:c r="O90" s="173"/>
       <x:c r="P90" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A90)&gt;0,"No",IF(E90="BECM 3204",IF(J90='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E90="BECM 3208",IF(J90='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E90="CE 3224",IF(J90='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E90="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C90,2)=1,"Yes","No"),IF(MOD(C90,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5567,28 +5612,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E91" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F91" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G91" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H91" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I91" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J91" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K91" s="131" t="str"/>
-      <x:c r="L91" s="143" t="str"/>
-      <x:c r="M91" s="143" t="str"/>
-      <x:c r="N91" s="143" t="str"/>
-      <x:c r="O91" s="173" t="str"/>
+      <x:c r="K91" s="131"/>
+      <x:c r="L91" s="143"/>
+      <x:c r="M91" s="143"/>
+      <x:c r="N91" s="143"/>
+      <x:c r="O91" s="173"/>
       <x:c r="P91" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A91)&gt;0,"No",IF(E91="BECM 3204",IF(J91='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E91="BECM 3208",IF(J91='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E91="CE 3224",IF(J91='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E91="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C91,2)=1,"Yes","No"),IF(MOD(C91,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5619,17 +5664,15 @@
       <x:c r="H92" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I92" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I92" s="23"/>
       <x:c r="J92" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K92" s="131" t="str"/>
-      <x:c r="L92" s="143" t="str"/>
-      <x:c r="M92" s="143" t="str"/>
-      <x:c r="N92" s="143" t="str"/>
-      <x:c r="O92" s="173" t="str"/>
+      <x:c r="K92" s="131"/>
+      <x:c r="L92" s="143"/>
+      <x:c r="M92" s="143"/>
+      <x:c r="N92" s="143"/>
+      <x:c r="O92" s="173"/>
       <x:c r="P92" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A92)&gt;0,"No",IF(E92="BECM 3204",IF(J92='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E92="BECM 3208",IF(J92='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E92="CE 3224",IF(J92='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E92="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C92,2)=1,"Yes","No"),IF(MOD(C92,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -5661,16 +5704,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I93" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J93" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K93" s="131" t="str"/>
-      <x:c r="L93" s="143" t="str"/>
-      <x:c r="M93" s="143" t="str"/>
-      <x:c r="N93" s="143" t="str"/>
-      <x:c r="O93" s="173" t="str"/>
+      <x:c r="K93" s="131"/>
+      <x:c r="L93" s="143"/>
+      <x:c r="M93" s="143"/>
+      <x:c r="N93" s="143"/>
+      <x:c r="O93" s="173"/>
       <x:c r="P93" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A93)&gt;0,"No",IF(E93="BECM 3204",IF(J93='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E93="BECM 3208",IF(J93='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E93="CE 3224",IF(J93='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E93="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C93,2)=1,"Yes","No"),IF(MOD(C93,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5690,28 +5733,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E94" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F94" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G94" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H94" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I94" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J94" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K94" s="131" t="str"/>
-      <x:c r="L94" s="143" t="str"/>
-      <x:c r="M94" s="143" t="str"/>
-      <x:c r="N94" s="143" t="str"/>
-      <x:c r="O94" s="173" t="str"/>
+      <x:c r="K94" s="131"/>
+      <x:c r="L94" s="143"/>
+      <x:c r="M94" s="143"/>
+      <x:c r="N94" s="143"/>
+      <x:c r="O94" s="173"/>
       <x:c r="P94" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A94)&gt;0,"No",IF(E94="BECM 3204",IF(J94='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E94="BECM 3208",IF(J94='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E94="CE 3224",IF(J94='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E94="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C94,2)=1,"Yes","No"),IF(MOD(C94,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5731,28 +5774,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E95" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F95" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G95" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H95" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I95" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J95" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K95" s="131" t="str"/>
-      <x:c r="L95" s="143" t="str"/>
-      <x:c r="M95" s="143" t="str"/>
-      <x:c r="N95" s="143" t="str"/>
-      <x:c r="O95" s="173" t="str"/>
+      <x:c r="K95" s="131"/>
+      <x:c r="L95" s="143"/>
+      <x:c r="M95" s="143"/>
+      <x:c r="N95" s="143"/>
+      <x:c r="O95" s="173"/>
       <x:c r="P95" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A95)&gt;0,"No",IF(E95="BECM 3204",IF(J95='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E95="BECM 3208",IF(J95='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E95="CE 3224",IF(J95='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E95="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C95,2)=1,"Yes","No"),IF(MOD(C95,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5783,17 +5826,15 @@
       <x:c r="H96" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I96" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I96" s="23"/>
       <x:c r="J96" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K96" s="131" t="str"/>
-      <x:c r="L96" s="143" t="str"/>
-      <x:c r="M96" s="143" t="str"/>
-      <x:c r="N96" s="143" t="str"/>
-      <x:c r="O96" s="173" t="str"/>
+      <x:c r="K96" s="131"/>
+      <x:c r="L96" s="143"/>
+      <x:c r="M96" s="143"/>
+      <x:c r="N96" s="143"/>
+      <x:c r="O96" s="173"/>
       <x:c r="P96" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A96)&gt;0,"No",IF(E96="BECM 3204",IF(J96='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E96="BECM 3208",IF(J96='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E96="CE 3224",IF(J96='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E96="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C96,2)=1,"Yes","No"),IF(MOD(C96,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5813,28 +5854,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E97" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F97" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G97" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H97" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I97" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J97" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K97" s="131" t="str"/>
-      <x:c r="L97" s="143" t="str"/>
-      <x:c r="M97" s="143" t="str"/>
-      <x:c r="N97" s="143" t="str"/>
-      <x:c r="O97" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K97" s="131"/>
+      <x:c r="L97" s="143"/>
+      <x:c r="M97" s="143"/>
+      <x:c r="N97" s="143"/>
+      <x:c r="O97" s="173"/>
       <x:c r="P97" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A97)&gt;0,"No",IF(E97="BECM 3204",IF(J97='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E97="BECM 3208",IF(J97='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E97="CE 3224",IF(J97='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E97="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C97,2)=1,"Yes","No"),IF(MOD(C97,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5866,16 +5907,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I98" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J98" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K98" s="131" t="str"/>
-      <x:c r="L98" s="143" t="str"/>
-      <x:c r="M98" s="143" t="str"/>
-      <x:c r="N98" s="143" t="str"/>
-      <x:c r="O98" s="173" t="str"/>
+      <x:c r="K98" s="131"/>
+      <x:c r="L98" s="143"/>
+      <x:c r="M98" s="143"/>
+      <x:c r="N98" s="143"/>
+      <x:c r="O98" s="173"/>
       <x:c r="P98" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A98)&gt;0,"No",IF(E98="BECM 3204",IF(J98='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E98="BECM 3208",IF(J98='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E98="CE 3224",IF(J98='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E98="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C98,2)=1,"Yes","No"),IF(MOD(C98,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5907,16 +5948,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I99" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J99" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K99" s="131" t="str"/>
-      <x:c r="L99" s="143" t="str"/>
-      <x:c r="M99" s="143" t="str"/>
-      <x:c r="N99" s="143" t="str"/>
-      <x:c r="O99" s="173" t="str"/>
+      <x:c r="K99" s="131"/>
+      <x:c r="L99" s="143"/>
+      <x:c r="M99" s="143"/>
+      <x:c r="N99" s="143"/>
+      <x:c r="O99" s="173"/>
       <x:c r="P99" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A99)&gt;0,"No",IF(E99="BECM 3204",IF(J99='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E99="BECM 3208",IF(J99='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E99="CE 3224",IF(J99='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E99="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C99,2)=1,"Yes","No"),IF(MOD(C99,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5936,26 +5977,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E100" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F100" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G100" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H100" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I100" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I100" s="23"/>
       <x:c r="J100" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K100" s="131" t="str"/>
-      <x:c r="L100" s="143" t="str"/>
-      <x:c r="M100" s="143" t="str"/>
-      <x:c r="N100" s="143" t="str"/>
-      <x:c r="O100" s="173" t="str"/>
+      <x:c r="K100" s="131"/>
+      <x:c r="L100" s="143"/>
+      <x:c r="M100" s="143"/>
+      <x:c r="N100" s="143"/>
+      <x:c r="O100" s="173"/>
       <x:c r="P100" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A100)&gt;0,"No",IF(E100="BECM 3204",IF(J100='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E100="BECM 3208",IF(J100='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E100="CE 3224",IF(J100='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E100="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C100,2)=1,"Yes","No"),IF(MOD(C100,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -5975,26 +6016,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E101" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F101" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G101" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H101" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I101" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I101" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J101" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K101" s="131" t="str"/>
-      <x:c r="L101" s="143" t="str"/>
-      <x:c r="M101" s="143" t="str"/>
-      <x:c r="N101" s="143" t="str"/>
-      <x:c r="O101" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K101" s="131"/>
+      <x:c r="L101" s="143"/>
+      <x:c r="M101" s="143"/>
+      <x:c r="N101" s="143"/>
+      <x:c r="O101" s="173"/>
       <x:c r="P101" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A101)&gt;0,"No",IF(E101="BECM 3204",IF(J101='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E101="BECM 3208",IF(J101='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E101="CE 3224",IF(J101='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E101="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C101,2)=1,"Yes","No"),IF(MOD(C101,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6014,28 +6057,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E102" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F102" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G102" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H102" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I102" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J102" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K102" s="131" t="str"/>
-      <x:c r="L102" s="143" t="str"/>
-      <x:c r="M102" s="143" t="str"/>
-      <x:c r="N102" s="143" t="str"/>
-      <x:c r="O102" s="173" t="str"/>
+      <x:c r="K102" s="131"/>
+      <x:c r="L102" s="143"/>
+      <x:c r="M102" s="143"/>
+      <x:c r="N102" s="143"/>
+      <x:c r="O102" s="173"/>
       <x:c r="P102" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A102)&gt;0,"No",IF(E102="BECM 3204",IF(J102='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E102="BECM 3208",IF(J102='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E102="CE 3224",IF(J102='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E102="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C102,2)=1,"Yes","No"),IF(MOD(C102,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6055,28 +6098,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E103" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F103" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G103" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H103" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I103" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J103" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K103" s="131" t="str"/>
-      <x:c r="L103" s="143" t="str"/>
-      <x:c r="M103" s="143" t="str"/>
-      <x:c r="N103" s="143" t="str"/>
-      <x:c r="O103" s="173" t="str"/>
+      <x:c r="K103" s="131"/>
+      <x:c r="L103" s="143"/>
+      <x:c r="M103" s="143"/>
+      <x:c r="N103" s="143"/>
+      <x:c r="O103" s="173"/>
       <x:c r="P103" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A103)&gt;0,"No",IF(E103="BECM 3204",IF(J103='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E103="BECM 3208",IF(J103='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E103="CE 3224",IF(J103='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E103="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C103,2)=1,"Yes","No"),IF(MOD(C103,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6096,26 +6139,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E104" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F104" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G104" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H104" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I104" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I104" s="23"/>
       <x:c r="J104" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K104" s="131" t="str"/>
-      <x:c r="L104" s="143" t="str"/>
-      <x:c r="M104" s="143" t="str"/>
-      <x:c r="N104" s="143" t="str"/>
-      <x:c r="O104" s="173" t="str"/>
+      <x:c r="K104" s="131"/>
+      <x:c r="L104" s="143"/>
+      <x:c r="M104" s="143"/>
+      <x:c r="N104" s="143"/>
+      <x:c r="O104" s="173"/>
       <x:c r="P104" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A104)&gt;0,"No",IF(E104="BECM 3204",IF(J104='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E104="BECM 3208",IF(J104='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E104="CE 3224",IF(J104='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E104="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C104,2)=1,"Yes","No"),IF(MOD(C104,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6135,31 +6178,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E105" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F105" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G105" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H105" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I105" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I105" s="23"/>
       <x:c r="J105" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K105" s="131" t="str"/>
-      <x:c r="L105" s="143" t="str"/>
-      <x:c r="M105" s="143" t="str"/>
-      <x:c r="N105" s="143" t="str"/>
-      <x:c r="O105" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K105" s="131"/>
+      <x:c r="L105" s="143"/>
+      <x:c r="M105" s="143"/>
+      <x:c r="N105" s="143"/>
+      <x:c r="O105" s="173"/>
       <x:c r="P105" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A105)&gt;0,"No",IF(E105="BECM 3204",IF(J105='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E105="BECM 3208",IF(J105='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E105="CE 3224",IF(J105='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E105="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C105,2)=1,"Yes","No"),IF(MOD(C105,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -6176,28 +6217,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E106" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F106" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G106" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H106" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I106" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J106" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K106" s="131" t="str"/>
-      <x:c r="L106" s="143" t="str"/>
-      <x:c r="M106" s="143" t="str"/>
-      <x:c r="N106" s="143" t="str"/>
-      <x:c r="O106" s="173" t="str"/>
+      <x:c r="K106" s="131"/>
+      <x:c r="L106" s="143"/>
+      <x:c r="M106" s="143"/>
+      <x:c r="N106" s="143"/>
+      <x:c r="O106" s="173"/>
       <x:c r="P106" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A106)&gt;0,"No",IF(E106="BECM 3204",IF(J106='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E106="BECM 3208",IF(J106='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E106="CE 3224",IF(J106='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E106="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C106,2)=1,"Yes","No"),IF(MOD(C106,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6217,28 +6258,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E107" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F107" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G107" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H107" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I107" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J107" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K107" s="131" t="str"/>
-      <x:c r="L107" s="143" t="str"/>
-      <x:c r="M107" s="143" t="str"/>
-      <x:c r="N107" s="143" t="str"/>
-      <x:c r="O107" s="173" t="str"/>
+      <x:c r="K107" s="131"/>
+      <x:c r="L107" s="143"/>
+      <x:c r="M107" s="143"/>
+      <x:c r="N107" s="143"/>
+      <x:c r="O107" s="173"/>
       <x:c r="P107" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A107)&gt;0,"No",IF(E107="BECM 3204",IF(J107='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E107="BECM 3208",IF(J107='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E107="CE 3224",IF(J107='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E107="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C107,2)=1,"Yes","No"),IF(MOD(C107,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6270,16 +6311,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I108" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J108" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K108" s="131" t="str"/>
-      <x:c r="L108" s="143" t="str"/>
-      <x:c r="M108" s="143" t="str"/>
-      <x:c r="N108" s="143" t="str"/>
-      <x:c r="O108" s="173" t="str"/>
+      <x:c r="K108" s="131"/>
+      <x:c r="L108" s="143"/>
+      <x:c r="M108" s="143"/>
+      <x:c r="N108" s="143"/>
+      <x:c r="O108" s="173"/>
       <x:c r="P108" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A108)&gt;0,"No",IF(E108="BECM 3204",IF(J108='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E108="BECM 3208",IF(J108='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E108="CE 3224",IF(J108='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E108="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C108,2)=1,"Yes","No"),IF(MOD(C108,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6299,28 +6340,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E109" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F109" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G109" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H109" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I109" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I109" s="23"/>
       <x:c r="J109" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K109" s="131" t="str"/>
-      <x:c r="L109" s="143" t="str"/>
-      <x:c r="M109" s="143" t="str"/>
-      <x:c r="N109" s="143" t="str"/>
-      <x:c r="O109" s="173" t="str"/>
+      <x:c r="K109" s="131"/>
+      <x:c r="L109" s="143"/>
+      <x:c r="M109" s="143"/>
+      <x:c r="N109" s="143"/>
+      <x:c r="O109" s="173"/>
       <x:c r="P109" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A109)&gt;0,"No",IF(E109="BECM 3204",IF(J109='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E109="BECM 3208",IF(J109='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E109="CE 3224",IF(J109='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E109="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C109,2)=1,"Yes","No"),IF(MOD(C109,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -6340,29 +6379,31 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E110" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F110" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G110" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H110" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I110" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I110" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J110" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K110" s="131" t="str"/>
-      <x:c r="L110" s="143" t="str"/>
-      <x:c r="M110" s="143" t="str"/>
-      <x:c r="N110" s="143" t="str"/>
-      <x:c r="O110" s="173" t="str"/>
+      <x:c r="K110" s="131"/>
+      <x:c r="L110" s="143"/>
+      <x:c r="M110" s="143"/>
+      <x:c r="N110" s="143"/>
+      <x:c r="O110" s="173"/>
       <x:c r="P110" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A110)&gt;0,"No",IF(E110="BECM 3204",IF(J110='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E110="BECM 3208",IF(J110='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E110="CE 3224",IF(J110='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E110="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C110,2)=1,"Yes","No"),IF(MOD(C110,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -6379,28 +6420,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E111" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F111" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G111" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H111" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I111" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J111" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K111" s="131" t="str"/>
-      <x:c r="L111" s="143" t="str"/>
-      <x:c r="M111" s="143" t="str"/>
-      <x:c r="N111" s="143" t="str"/>
-      <x:c r="O111" s="173" t="str"/>
+      <x:c r="K111" s="131"/>
+      <x:c r="L111" s="143"/>
+      <x:c r="M111" s="143"/>
+      <x:c r="N111" s="143"/>
+      <x:c r="O111" s="173"/>
       <x:c r="P111" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A111)&gt;0,"No",IF(E111="BECM 3204",IF(J111='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E111="BECM 3208",IF(J111='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E111="CE 3224",IF(J111='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E111="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C111,2)=1,"Yes","No"),IF(MOD(C111,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6420,28 +6461,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E112" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F112" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G112" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H112" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I112" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J112" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K112" s="131" t="str"/>
-      <x:c r="L112" s="143" t="str"/>
-      <x:c r="M112" s="143" t="str"/>
-      <x:c r="N112" s="143" t="str"/>
-      <x:c r="O112" s="173" t="str"/>
+      <x:c r="K112" s="131"/>
+      <x:c r="L112" s="143"/>
+      <x:c r="M112" s="143"/>
+      <x:c r="N112" s="143"/>
+      <x:c r="O112" s="173"/>
       <x:c r="P112" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A112)&gt;0,"No",IF(E112="BECM 3204",IF(J112='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E112="BECM 3208",IF(J112='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E112="CE 3224",IF(J112='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E112="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C112,2)=1,"Yes","No"),IF(MOD(C112,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6461,28 +6502,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E113" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F113" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G113" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H113" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I113" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J113" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K113" s="131" t="str"/>
-      <x:c r="L113" s="143" t="str"/>
-      <x:c r="M113" s="143" t="str"/>
-      <x:c r="N113" s="143" t="str"/>
-      <x:c r="O113" s="173" t="str"/>
+      <x:c r="K113" s="131"/>
+      <x:c r="L113" s="143"/>
+      <x:c r="M113" s="143"/>
+      <x:c r="N113" s="143"/>
+      <x:c r="O113" s="173"/>
       <x:c r="P113" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A113)&gt;0,"No",IF(E113="BECM 3204",IF(J113='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E113="BECM 3208",IF(J113='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E113="CE 3224",IF(J113='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E113="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C113,2)=1,"Yes","No"),IF(MOD(C113,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6513,17 +6554,15 @@
       <x:c r="H114" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I114" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I114" s="23"/>
       <x:c r="J114" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K114" s="131" t="str"/>
-      <x:c r="L114" s="143" t="str"/>
-      <x:c r="M114" s="143" t="str"/>
-      <x:c r="N114" s="143" t="str"/>
-      <x:c r="O114" s="173" t="str"/>
+      <x:c r="K114" s="131"/>
+      <x:c r="L114" s="143"/>
+      <x:c r="M114" s="143"/>
+      <x:c r="N114" s="143"/>
+      <x:c r="O114" s="173"/>
       <x:c r="P114" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A114)&gt;0,"No",IF(E114="BECM 3204",IF(J114='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E114="BECM 3208",IF(J114='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E114="CE 3224",IF(J114='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E114="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C114,2)=1,"Yes","No"),IF(MOD(C114,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -6555,16 +6594,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I115" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J115" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K115" s="131" t="str"/>
-      <x:c r="L115" s="143" t="str"/>
-      <x:c r="M115" s="143" t="str"/>
-      <x:c r="N115" s="143" t="str"/>
-      <x:c r="O115" s="173" t="str"/>
+      <x:c r="K115" s="131"/>
+      <x:c r="L115" s="143"/>
+      <x:c r="M115" s="143"/>
+      <x:c r="N115" s="143"/>
+      <x:c r="O115" s="173"/>
       <x:c r="P115" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A115)&gt;0,"No",IF(E115="BECM 3204",IF(J115='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E115="BECM 3208",IF(J115='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E115="CE 3224",IF(J115='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E115="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C115,2)=1,"Yes","No"),IF(MOD(C115,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6584,28 +6623,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E116" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F116" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G116" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H116" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I116" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J116" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K116" s="131" t="str"/>
-      <x:c r="L116" s="143" t="str"/>
-      <x:c r="M116" s="143" t="str"/>
-      <x:c r="N116" s="143" t="str"/>
-      <x:c r="O116" s="173" t="str"/>
+      <x:c r="K116" s="131"/>
+      <x:c r="L116" s="143"/>
+      <x:c r="M116" s="143"/>
+      <x:c r="N116" s="143"/>
+      <x:c r="O116" s="173"/>
       <x:c r="P116" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A116)&gt;0,"No",IF(E116="BECM 3204",IF(J116='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E116="BECM 3208",IF(J116='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E116="CE 3224",IF(J116='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E116="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C116,2)=1,"Yes","No"),IF(MOD(C116,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6625,28 +6664,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E117" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F117" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G117" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H117" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I117" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J117" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K117" s="131" t="str"/>
-      <x:c r="L117" s="143" t="str"/>
-      <x:c r="M117" s="143" t="str"/>
-      <x:c r="N117" s="143" t="str"/>
-      <x:c r="O117" s="173" t="str"/>
+      <x:c r="K117" s="131"/>
+      <x:c r="L117" s="143"/>
+      <x:c r="M117" s="143"/>
+      <x:c r="N117" s="143"/>
+      <x:c r="O117" s="173"/>
       <x:c r="P117" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A117)&gt;0,"No",IF(E117="BECM 3204",IF(J117='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E117="BECM 3208",IF(J117='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E117="CE 3224",IF(J117='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E117="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C117,2)=1,"Yes","No"),IF(MOD(C117,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6677,17 +6716,15 @@
       <x:c r="H118" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I118" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I118" s="23"/>
       <x:c r="J118" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K118" s="131" t="str"/>
-      <x:c r="L118" s="143" t="str"/>
-      <x:c r="M118" s="143" t="str"/>
-      <x:c r="N118" s="143" t="str"/>
-      <x:c r="O118" s="173" t="str"/>
+      <x:c r="K118" s="131"/>
+      <x:c r="L118" s="143"/>
+      <x:c r="M118" s="143"/>
+      <x:c r="N118" s="143"/>
+      <x:c r="O118" s="173"/>
       <x:c r="P118" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A118)&gt;0,"No",IF(E118="BECM 3204",IF(J118='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E118="BECM 3208",IF(J118='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E118="CE 3224",IF(J118='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E118="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C118,2)=1,"Yes","No"),IF(MOD(C118,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6707,28 +6744,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E119" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F119" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G119" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H119" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I119" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J119" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K119" s="131" t="str"/>
-      <x:c r="L119" s="143" t="str"/>
-      <x:c r="M119" s="143" t="str"/>
-      <x:c r="N119" s="143" t="str"/>
-      <x:c r="O119" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K119" s="131"/>
+      <x:c r="L119" s="143"/>
+      <x:c r="M119" s="143"/>
+      <x:c r="N119" s="143"/>
+      <x:c r="O119" s="173"/>
       <x:c r="P119" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A119)&gt;0,"No",IF(E119="BECM 3204",IF(J119='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E119="BECM 3208",IF(J119='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E119="CE 3224",IF(J119='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E119="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C119,2)=1,"Yes","No"),IF(MOD(C119,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6760,16 +6797,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I120" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J120" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K120" s="131" t="str"/>
-      <x:c r="L120" s="143" t="str"/>
-      <x:c r="M120" s="143" t="str"/>
-      <x:c r="N120" s="143" t="str"/>
-      <x:c r="O120" s="173" t="str"/>
+      <x:c r="K120" s="131"/>
+      <x:c r="L120" s="143"/>
+      <x:c r="M120" s="143"/>
+      <x:c r="N120" s="143"/>
+      <x:c r="O120" s="173"/>
       <x:c r="P120" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A120)&gt;0,"No",IF(E120="BECM 3204",IF(J120='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E120="BECM 3208",IF(J120='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E120="CE 3224",IF(J120='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E120="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C120,2)=1,"Yes","No"),IF(MOD(C120,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6801,16 +6838,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I121" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J121" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K121" s="131" t="str"/>
-      <x:c r="L121" s="143" t="str"/>
-      <x:c r="M121" s="143" t="str"/>
-      <x:c r="N121" s="143" t="str"/>
-      <x:c r="O121" s="173" t="str"/>
+      <x:c r="K121" s="131"/>
+      <x:c r="L121" s="143"/>
+      <x:c r="M121" s="143"/>
+      <x:c r="N121" s="143"/>
+      <x:c r="O121" s="173"/>
       <x:c r="P121" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A121)&gt;0,"No",IF(E121="BECM 3204",IF(J121='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E121="BECM 3208",IF(J121='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E121="CE 3224",IF(J121='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E121="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C121,2)=1,"Yes","No"),IF(MOD(C121,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6830,29 +6867,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E122" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F122" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G122" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H122" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I122" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I122" s="23"/>
       <x:c r="J122" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K122" s="131" t="str"/>
-      <x:c r="L122" s="143" t="str"/>
-      <x:c r="M122" s="143" t="str"/>
-      <x:c r="N122" s="143" t="str"/>
-      <x:c r="O122" s="173" t="str"/>
+      <x:c r="K122" s="131"/>
+      <x:c r="L122" s="143"/>
+      <x:c r="M122" s="143"/>
+      <x:c r="N122" s="143"/>
+      <x:c r="O122" s="173"/>
       <x:c r="P122" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A122)&gt;0,"No",IF(E122="BECM 3204",IF(J122='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E122="BECM 3208",IF(J122='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E122="CE 3224",IF(J122='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E122="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C122,2)=1,"Yes","No"),IF(MOD(C122,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -6869,26 +6906,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E123" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F123" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G123" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H123" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I123" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I123" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J123" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K123" s="131" t="str"/>
-      <x:c r="L123" s="143" t="str"/>
-      <x:c r="M123" s="143" t="str"/>
-      <x:c r="N123" s="143" t="str"/>
-      <x:c r="O123" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K123" s="131"/>
+      <x:c r="L123" s="143"/>
+      <x:c r="M123" s="143"/>
+      <x:c r="N123" s="143"/>
+      <x:c r="O123" s="173"/>
       <x:c r="P123" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A123)&gt;0,"No",IF(E123="BECM 3204",IF(J123='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E123="BECM 3208",IF(J123='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E123="CE 3224",IF(J123='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E123="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C123,2)=1,"Yes","No"),IF(MOD(C123,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6908,28 +6947,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E124" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F124" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G124" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H124" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I124" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J124" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K124" s="131" t="str"/>
-      <x:c r="L124" s="143" t="str"/>
-      <x:c r="M124" s="143" t="str"/>
-      <x:c r="N124" s="143" t="str"/>
-      <x:c r="O124" s="173" t="str"/>
+      <x:c r="K124" s="131"/>
+      <x:c r="L124" s="143"/>
+      <x:c r="M124" s="143"/>
+      <x:c r="N124" s="143"/>
+      <x:c r="O124" s="173"/>
       <x:c r="P124" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A124)&gt;0,"No",IF(E124="BECM 3204",IF(J124='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E124="BECM 3208",IF(J124='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E124="CE 3224",IF(J124='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E124="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C124,2)=1,"Yes","No"),IF(MOD(C124,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6949,28 +6988,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E125" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F125" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G125" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H125" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I125" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J125" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K125" s="131" t="str"/>
-      <x:c r="L125" s="143" t="str"/>
-      <x:c r="M125" s="143" t="str"/>
-      <x:c r="N125" s="143" t="str"/>
-      <x:c r="O125" s="173" t="str"/>
+      <x:c r="K125" s="131"/>
+      <x:c r="L125" s="143"/>
+      <x:c r="M125" s="143"/>
+      <x:c r="N125" s="143"/>
+      <x:c r="O125" s="173"/>
       <x:c r="P125" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A125)&gt;0,"No",IF(E125="BECM 3204",IF(J125='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E125="BECM 3208",IF(J125='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E125="CE 3224",IF(J125='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E125="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C125,2)=1,"Yes","No"),IF(MOD(C125,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -6990,26 +7029,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E126" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F126" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G126" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H126" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I126" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I126" s="23"/>
       <x:c r="J126" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K126" s="131" t="str"/>
-      <x:c r="L126" s="143" t="str"/>
-      <x:c r="M126" s="143" t="str"/>
-      <x:c r="N126" s="143" t="str"/>
-      <x:c r="O126" s="173" t="str"/>
+      <x:c r="K126" s="131"/>
+      <x:c r="L126" s="143"/>
+      <x:c r="M126" s="143"/>
+      <x:c r="N126" s="143"/>
+      <x:c r="O126" s="173"/>
       <x:c r="P126" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A126)&gt;0,"No",IF(E126="BECM 3204",IF(J126='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E126="BECM 3208",IF(J126='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E126="CE 3224",IF(J126='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E126="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C126,2)=1,"Yes","No"),IF(MOD(C126,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7029,31 +7068,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E127" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F127" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G127" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H127" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I127" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I127" s="23"/>
       <x:c r="J127" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K127" s="131" t="str"/>
-      <x:c r="L127" s="143" t="str"/>
-      <x:c r="M127" s="143" t="str"/>
-      <x:c r="N127" s="143" t="str"/>
-      <x:c r="O127" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K127" s="131"/>
+      <x:c r="L127" s="143"/>
+      <x:c r="M127" s="143"/>
+      <x:c r="N127" s="143"/>
+      <x:c r="O127" s="173"/>
       <x:c r="P127" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A127)&gt;0,"No",IF(E127="BECM 3204",IF(J127='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E127="BECM 3208",IF(J127='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E127="CE 3224",IF(J127='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E127="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C127,2)=1,"Yes","No"),IF(MOD(C127,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -7070,28 +7107,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E128" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F128" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G128" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H128" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I128" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J128" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K128" s="131" t="str"/>
-      <x:c r="L128" s="143" t="str"/>
-      <x:c r="M128" s="143" t="str"/>
-      <x:c r="N128" s="143" t="str"/>
-      <x:c r="O128" s="173" t="str"/>
+      <x:c r="K128" s="131"/>
+      <x:c r="L128" s="143"/>
+      <x:c r="M128" s="143"/>
+      <x:c r="N128" s="143"/>
+      <x:c r="O128" s="173"/>
       <x:c r="P128" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A128)&gt;0,"No",IF(E128="BECM 3204",IF(J128='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E128="BECM 3208",IF(J128='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E128="CE 3224",IF(J128='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E128="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C128,2)=1,"Yes","No"),IF(MOD(C128,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7111,28 +7148,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E129" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F129" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G129" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H129" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I129" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J129" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K129" s="131" t="str"/>
-      <x:c r="L129" s="143" t="str"/>
-      <x:c r="M129" s="143" t="str"/>
-      <x:c r="N129" s="143" t="str"/>
-      <x:c r="O129" s="173" t="str"/>
+      <x:c r="K129" s="131"/>
+      <x:c r="L129" s="143"/>
+      <x:c r="M129" s="143"/>
+      <x:c r="N129" s="143"/>
+      <x:c r="O129" s="173"/>
       <x:c r="P129" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A129)&gt;0,"No",IF(E129="BECM 3204",IF(J129='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E129="BECM 3208",IF(J129='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E129="CE 3224",IF(J129='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E129="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C129,2)=1,"Yes","No"),IF(MOD(C129,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7164,16 +7201,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I130" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J130" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K130" s="131" t="str"/>
-      <x:c r="L130" s="143" t="str"/>
-      <x:c r="M130" s="143" t="str"/>
-      <x:c r="N130" s="143" t="str"/>
-      <x:c r="O130" s="173" t="str"/>
+      <x:c r="K130" s="131"/>
+      <x:c r="L130" s="143"/>
+      <x:c r="M130" s="143"/>
+      <x:c r="N130" s="143"/>
+      <x:c r="O130" s="173"/>
       <x:c r="P130" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A130)&gt;0,"No",IF(E130="BECM 3204",IF(J130='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E130="BECM 3208",IF(J130='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E130="CE 3224",IF(J130='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E130="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C130,2)=1,"Yes","No"),IF(MOD(C130,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7193,28 +7230,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E131" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F131" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G131" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H131" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I131" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I131" s="23"/>
       <x:c r="J131" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K131" s="131" t="str"/>
-      <x:c r="L131" s="143" t="str"/>
-      <x:c r="M131" s="143" t="str"/>
-      <x:c r="N131" s="143" t="str"/>
-      <x:c r="O131" s="173" t="str"/>
+      <x:c r="K131" s="131"/>
+      <x:c r="L131" s="143"/>
+      <x:c r="M131" s="143"/>
+      <x:c r="N131" s="143"/>
+      <x:c r="O131" s="173"/>
       <x:c r="P131" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A131)&gt;0,"No",IF(E131="BECM 3204",IF(J131='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E131="BECM 3208",IF(J131='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E131="CE 3224",IF(J131='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E131="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C131,2)=1,"Yes","No"),IF(MOD(C131,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -7234,26 +7269,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E132" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F132" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G132" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H132" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I132" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I132" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J132" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K132" s="131" t="str"/>
-      <x:c r="L132" s="143" t="str"/>
-      <x:c r="M132" s="143" t="str"/>
-      <x:c r="N132" s="143" t="str"/>
-      <x:c r="O132" s="173" t="str"/>
+      <x:c r="K132" s="131"/>
+      <x:c r="L132" s="143"/>
+      <x:c r="M132" s="143"/>
+      <x:c r="N132" s="143"/>
+      <x:c r="O132" s="173"/>
       <x:c r="P132" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A132)&gt;0,"No",IF(E132="BECM 3204",IF(J132='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E132="BECM 3208",IF(J132='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E132="CE 3224",IF(J132='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E132="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C132,2)=1,"Yes","No"),IF(MOD(C132,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -7273,28 +7310,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E133" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F133" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G133" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H133" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I133" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J133" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K133" s="131" t="str"/>
-      <x:c r="L133" s="143" t="str"/>
-      <x:c r="M133" s="143" t="str"/>
-      <x:c r="N133" s="143" t="str"/>
-      <x:c r="O133" s="173" t="str"/>
+      <x:c r="K133" s="131"/>
+      <x:c r="L133" s="143"/>
+      <x:c r="M133" s="143"/>
+      <x:c r="N133" s="143"/>
+      <x:c r="O133" s="173"/>
       <x:c r="P133" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A133)&gt;0,"No",IF(E133="BECM 3204",IF(J133='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E133="BECM 3208",IF(J133='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E133="CE 3224",IF(J133='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E133="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C133,2)=1,"Yes","No"),IF(MOD(C133,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7314,28 +7351,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E134" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F134" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G134" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H134" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I134" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J134" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K134" s="131" t="str"/>
-      <x:c r="L134" s="143" t="str"/>
-      <x:c r="M134" s="143" t="str"/>
-      <x:c r="N134" s="143" t="str"/>
-      <x:c r="O134" s="173" t="str"/>
+      <x:c r="K134" s="131"/>
+      <x:c r="L134" s="143"/>
+      <x:c r="M134" s="143"/>
+      <x:c r="N134" s="143"/>
+      <x:c r="O134" s="173"/>
       <x:c r="P134" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A134)&gt;0,"No",IF(E134="BECM 3204",IF(J134='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E134="BECM 3208",IF(J134='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E134="CE 3224",IF(J134='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E134="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C134,2)=1,"Yes","No"),IF(MOD(C134,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7355,28 +7392,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E135" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F135" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G135" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H135" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I135" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J135" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K135" s="131" t="str"/>
-      <x:c r="L135" s="143" t="str"/>
-      <x:c r="M135" s="143" t="str"/>
-      <x:c r="N135" s="143" t="str"/>
-      <x:c r="O135" s="173" t="str"/>
+      <x:c r="K135" s="131"/>
+      <x:c r="L135" s="143"/>
+      <x:c r="M135" s="143"/>
+      <x:c r="N135" s="143"/>
+      <x:c r="O135" s="173"/>
       <x:c r="P135" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A135)&gt;0,"No",IF(E135="BECM 3204",IF(J135='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E135="BECM 3208",IF(J135='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E135="CE 3224",IF(J135='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E135="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C135,2)=1,"Yes","No"),IF(MOD(C135,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7407,17 +7444,15 @@
       <x:c r="H136" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I136" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I136" s="23"/>
       <x:c r="J136" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K136" s="131" t="str"/>
-      <x:c r="L136" s="143" t="str"/>
-      <x:c r="M136" s="143" t="str"/>
-      <x:c r="N136" s="143" t="str"/>
-      <x:c r="O136" s="173" t="str"/>
+      <x:c r="K136" s="131"/>
+      <x:c r="L136" s="143"/>
+      <x:c r="M136" s="143"/>
+      <x:c r="N136" s="143"/>
+      <x:c r="O136" s="173"/>
       <x:c r="P136" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A136)&gt;0,"No",IF(E136="BECM 3204",IF(J136='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E136="BECM 3208",IF(J136='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E136="CE 3224",IF(J136='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E136="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C136,2)=1,"Yes","No"),IF(MOD(C136,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -7449,16 +7484,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I137" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J137" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K137" s="131" t="str"/>
-      <x:c r="L137" s="143" t="str"/>
-      <x:c r="M137" s="143" t="str"/>
-      <x:c r="N137" s="143" t="str"/>
-      <x:c r="O137" s="173" t="str"/>
+      <x:c r="K137" s="131"/>
+      <x:c r="L137" s="143"/>
+      <x:c r="M137" s="143"/>
+      <x:c r="N137" s="143"/>
+      <x:c r="O137" s="173"/>
       <x:c r="P137" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A137)&gt;0,"No",IF(E137="BECM 3204",IF(J137='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E137="BECM 3208",IF(J137='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E137="CE 3224",IF(J137='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E137="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C137,2)=1,"Yes","No"),IF(MOD(C137,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7478,28 +7513,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E138" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F138" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G138" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H138" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I138" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J138" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K138" s="131" t="str"/>
-      <x:c r="L138" s="143" t="str"/>
-      <x:c r="M138" s="143" t="str"/>
-      <x:c r="N138" s="143" t="str"/>
-      <x:c r="O138" s="173" t="str"/>
+      <x:c r="K138" s="131"/>
+      <x:c r="L138" s="143"/>
+      <x:c r="M138" s="143"/>
+      <x:c r="N138" s="143"/>
+      <x:c r="O138" s="173"/>
       <x:c r="P138" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A138)&gt;0,"No",IF(E138="BECM 3204",IF(J138='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E138="BECM 3208",IF(J138='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E138="CE 3224",IF(J138='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E138="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C138,2)=1,"Yes","No"),IF(MOD(C138,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7519,28 +7554,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E139" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F139" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G139" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H139" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I139" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J139" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K139" s="131" t="str"/>
-      <x:c r="L139" s="143" t="str"/>
-      <x:c r="M139" s="143" t="str"/>
-      <x:c r="N139" s="143" t="str"/>
-      <x:c r="O139" s="173" t="str"/>
+      <x:c r="K139" s="131"/>
+      <x:c r="L139" s="143"/>
+      <x:c r="M139" s="143"/>
+      <x:c r="N139" s="143"/>
+      <x:c r="O139" s="173"/>
       <x:c r="P139" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A139)&gt;0,"No",IF(E139="BECM 3204",IF(J139='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E139="BECM 3208",IF(J139='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E139="CE 3224",IF(J139='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E139="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C139,2)=1,"Yes","No"),IF(MOD(C139,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7571,17 +7606,15 @@
       <x:c r="H140" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I140" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I140" s="23"/>
       <x:c r="J140" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K140" s="131" t="str"/>
-      <x:c r="L140" s="143" t="str"/>
-      <x:c r="M140" s="143" t="str"/>
-      <x:c r="N140" s="143" t="str"/>
-      <x:c r="O140" s="173" t="str"/>
+      <x:c r="K140" s="131"/>
+      <x:c r="L140" s="143"/>
+      <x:c r="M140" s="143"/>
+      <x:c r="N140" s="143"/>
+      <x:c r="O140" s="173"/>
       <x:c r="P140" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A140)&gt;0,"No",IF(E140="BECM 3204",IF(J140='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E140="BECM 3208",IF(J140='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E140="CE 3224",IF(J140='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E140="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C140,2)=1,"Yes","No"),IF(MOD(C140,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7601,28 +7634,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E141" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F141" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G141" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H141" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I141" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J141" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K141" s="131" t="str"/>
-      <x:c r="L141" s="143" t="str"/>
-      <x:c r="M141" s="143" t="str"/>
-      <x:c r="N141" s="143" t="str"/>
-      <x:c r="O141" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K141" s="131"/>
+      <x:c r="L141" s="143"/>
+      <x:c r="M141" s="143"/>
+      <x:c r="N141" s="143"/>
+      <x:c r="O141" s="173"/>
       <x:c r="P141" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A141)&gt;0,"No",IF(E141="BECM 3204",IF(J141='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E141="BECM 3208",IF(J141='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E141="CE 3224",IF(J141='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E141="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C141,2)=1,"Yes","No"),IF(MOD(C141,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7654,16 +7687,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I142" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J142" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K142" s="131" t="str"/>
-      <x:c r="L142" s="143" t="str"/>
-      <x:c r="M142" s="143" t="str"/>
-      <x:c r="N142" s="143" t="str"/>
-      <x:c r="O142" s="173" t="str"/>
+      <x:c r="K142" s="131"/>
+      <x:c r="L142" s="143"/>
+      <x:c r="M142" s="143"/>
+      <x:c r="N142" s="143"/>
+      <x:c r="O142" s="173"/>
       <x:c r="P142" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A142)&gt;0,"No",IF(E142="BECM 3204",IF(J142='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E142="BECM 3208",IF(J142='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E142="CE 3224",IF(J142='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E142="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C142,2)=1,"Yes","No"),IF(MOD(C142,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7695,16 +7728,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I143" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J143" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K143" s="131" t="str"/>
-      <x:c r="L143" s="143" t="str"/>
-      <x:c r="M143" s="143" t="str"/>
-      <x:c r="N143" s="143" t="str"/>
-      <x:c r="O143" s="173" t="str"/>
+      <x:c r="K143" s="131"/>
+      <x:c r="L143" s="143"/>
+      <x:c r="M143" s="143"/>
+      <x:c r="N143" s="143"/>
+      <x:c r="O143" s="173"/>
       <x:c r="P143" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A143)&gt;0,"No",IF(E143="BECM 3204",IF(J143='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E143="BECM 3208",IF(J143='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E143="CE 3224",IF(J143='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E143="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C143,2)=1,"Yes","No"),IF(MOD(C143,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7724,26 +7757,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E144" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F144" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G144" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H144" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I144" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I144" s="23"/>
       <x:c r="J144" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K144" s="131" t="str"/>
-      <x:c r="L144" s="143" t="str"/>
-      <x:c r="M144" s="143" t="str"/>
-      <x:c r="N144" s="143" t="str"/>
-      <x:c r="O144" s="173" t="str"/>
+      <x:c r="K144" s="131"/>
+      <x:c r="L144" s="143"/>
+      <x:c r="M144" s="143"/>
+      <x:c r="N144" s="143"/>
+      <x:c r="O144" s="173"/>
       <x:c r="P144" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A144)&gt;0,"No",IF(E144="BECM 3204",IF(J144='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E144="BECM 3208",IF(J144='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E144="CE 3224",IF(J144='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E144="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C144,2)=1,"Yes","No"),IF(MOD(C144,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7763,26 +7796,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E145" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F145" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G145" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H145" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I145" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I145" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J145" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K145" s="131" t="str"/>
-      <x:c r="L145" s="143" t="str"/>
-      <x:c r="M145" s="143" t="str"/>
-      <x:c r="N145" s="143" t="str"/>
-      <x:c r="O145" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K145" s="131"/>
+      <x:c r="L145" s="143"/>
+      <x:c r="M145" s="143"/>
+      <x:c r="N145" s="143"/>
+      <x:c r="O145" s="173"/>
       <x:c r="P145" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A145)&gt;0,"No",IF(E145="BECM 3204",IF(J145='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E145="BECM 3208",IF(J145='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E145="CE 3224",IF(J145='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E145="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C145,2)=1,"Yes","No"),IF(MOD(C145,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7802,28 +7837,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E146" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F146" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G146" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H146" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I146" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J146" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K146" s="131" t="str"/>
-      <x:c r="L146" s="143" t="str"/>
-      <x:c r="M146" s="143" t="str"/>
-      <x:c r="N146" s="143" t="str"/>
-      <x:c r="O146" s="173" t="str"/>
+      <x:c r="K146" s="131"/>
+      <x:c r="L146" s="143"/>
+      <x:c r="M146" s="143"/>
+      <x:c r="N146" s="143"/>
+      <x:c r="O146" s="173"/>
       <x:c r="P146" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A146)&gt;0,"No",IF(E146="BECM 3204",IF(J146='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E146="BECM 3208",IF(J146='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E146="CE 3224",IF(J146='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E146="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C146,2)=1,"Yes","No"),IF(MOD(C146,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7843,28 +7878,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E147" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F147" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G147" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H147" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I147" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J147" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K147" s="131" t="str"/>
-      <x:c r="L147" s="143" t="str"/>
-      <x:c r="M147" s="143" t="str"/>
-      <x:c r="N147" s="143" t="str"/>
-      <x:c r="O147" s="173" t="str"/>
+      <x:c r="K147" s="131"/>
+      <x:c r="L147" s="143"/>
+      <x:c r="M147" s="143"/>
+      <x:c r="N147" s="143"/>
+      <x:c r="O147" s="173"/>
       <x:c r="P147" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A147)&gt;0,"No",IF(E147="BECM 3204",IF(J147='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E147="BECM 3208",IF(J147='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E147="CE 3224",IF(J147='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E147="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C147,2)=1,"Yes","No"),IF(MOD(C147,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7884,26 +7919,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E148" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F148" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G148" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H148" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I148" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I148" s="23"/>
       <x:c r="J148" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K148" s="131" t="str"/>
-      <x:c r="L148" s="143" t="str"/>
-      <x:c r="M148" s="143" t="str"/>
-      <x:c r="N148" s="143" t="str"/>
-      <x:c r="O148" s="173" t="str"/>
+      <x:c r="K148" s="131"/>
+      <x:c r="L148" s="143"/>
+      <x:c r="M148" s="143"/>
+      <x:c r="N148" s="143"/>
+      <x:c r="O148" s="173"/>
       <x:c r="P148" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A148)&gt;0,"No",IF(E148="BECM 3204",IF(J148='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E148="BECM 3208",IF(J148='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E148="CE 3224",IF(J148='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E148="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C148,2)=1,"Yes","No"),IF(MOD(C148,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -7923,31 +7958,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E149" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F149" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G149" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H149" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I149" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I149" s="23"/>
       <x:c r="J149" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K149" s="131" t="str"/>
-      <x:c r="L149" s="143" t="str"/>
-      <x:c r="M149" s="143" t="str"/>
-      <x:c r="N149" s="143" t="str"/>
-      <x:c r="O149" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K149" s="131"/>
+      <x:c r="L149" s="143"/>
+      <x:c r="M149" s="143"/>
+      <x:c r="N149" s="143"/>
+      <x:c r="O149" s="173"/>
       <x:c r="P149" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A149)&gt;0,"No",IF(E149="BECM 3204",IF(J149='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E149="BECM 3208",IF(J149='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E149="CE 3224",IF(J149='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E149="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C149,2)=1,"Yes","No"),IF(MOD(C149,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -7964,28 +7997,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E150" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F150" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G150" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H150" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I150" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J150" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K150" s="131" t="str"/>
-      <x:c r="L150" s="143" t="str"/>
-      <x:c r="M150" s="143" t="str"/>
-      <x:c r="N150" s="143" t="str"/>
-      <x:c r="O150" s="173" t="str"/>
+      <x:c r="K150" s="131"/>
+      <x:c r="L150" s="143"/>
+      <x:c r="M150" s="143"/>
+      <x:c r="N150" s="143"/>
+      <x:c r="O150" s="173"/>
       <x:c r="P150" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A150)&gt;0,"No",IF(E150="BECM 3204",IF(J150='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E150="BECM 3208",IF(J150='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E150="CE 3224",IF(J150='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E150="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C150,2)=1,"Yes","No"),IF(MOD(C150,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8005,28 +8038,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E151" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F151" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G151" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H151" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I151" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J151" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K151" s="131" t="str"/>
-      <x:c r="L151" s="143" t="str"/>
-      <x:c r="M151" s="143" t="str"/>
-      <x:c r="N151" s="143" t="str"/>
-      <x:c r="O151" s="173" t="str"/>
+      <x:c r="K151" s="131"/>
+      <x:c r="L151" s="143"/>
+      <x:c r="M151" s="143"/>
+      <x:c r="N151" s="143"/>
+      <x:c r="O151" s="173"/>
       <x:c r="P151" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A151)&gt;0,"No",IF(E151="BECM 3204",IF(J151='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E151="BECM 3208",IF(J151='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E151="CE 3224",IF(J151='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E151="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C151,2)=1,"Yes","No"),IF(MOD(C151,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8058,16 +8091,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I152" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J152" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K152" s="131" t="str"/>
-      <x:c r="L152" s="143" t="str"/>
-      <x:c r="M152" s="143" t="str"/>
-      <x:c r="N152" s="143" t="str"/>
-      <x:c r="O152" s="173" t="str"/>
+      <x:c r="K152" s="131"/>
+      <x:c r="L152" s="143"/>
+      <x:c r="M152" s="143"/>
+      <x:c r="N152" s="143"/>
+      <x:c r="O152" s="173"/>
       <x:c r="P152" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A152)&gt;0,"No",IF(E152="BECM 3204",IF(J152='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E152="BECM 3208",IF(J152='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E152="CE 3224",IF(J152='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E152="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C152,2)=1,"Yes","No"),IF(MOD(C152,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8087,28 +8120,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E153" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F153" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G153" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H153" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I153" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I153" s="23"/>
       <x:c r="J153" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K153" s="131" t="str"/>
-      <x:c r="L153" s="143" t="str"/>
-      <x:c r="M153" s="143" t="str"/>
-      <x:c r="N153" s="143" t="str"/>
-      <x:c r="O153" s="173" t="str"/>
+      <x:c r="K153" s="131"/>
+      <x:c r="L153" s="143"/>
+      <x:c r="M153" s="143"/>
+      <x:c r="N153" s="143"/>
+      <x:c r="O153" s="173"/>
       <x:c r="P153" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A153)&gt;0,"No",IF(E153="BECM 3204",IF(J153='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E153="BECM 3208",IF(J153='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E153="CE 3224",IF(J153='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E153="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C153,2)=1,"Yes","No"),IF(MOD(C153,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -8128,29 +8159,31 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E154" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F154" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G154" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H154" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I154" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I154" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J154" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K154" s="131" t="str"/>
-      <x:c r="L154" s="143" t="str"/>
-      <x:c r="M154" s="143" t="str"/>
-      <x:c r="N154" s="143" t="str"/>
-      <x:c r="O154" s="173" t="str"/>
+      <x:c r="K154" s="131"/>
+      <x:c r="L154" s="143"/>
+      <x:c r="M154" s="143"/>
+      <x:c r="N154" s="143"/>
+      <x:c r="O154" s="173"/>
       <x:c r="P154" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A154)&gt;0,"No",IF(E154="BECM 3204",IF(J154='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E154="BECM 3208",IF(J154='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E154="CE 3224",IF(J154='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E154="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C154,2)=1,"Yes","No"),IF(MOD(C154,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -8167,28 +8200,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E155" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F155" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G155" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H155" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I155" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J155" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K155" s="131" t="str"/>
-      <x:c r="L155" s="143" t="str"/>
-      <x:c r="M155" s="143" t="str"/>
-      <x:c r="N155" s="143" t="str"/>
-      <x:c r="O155" s="173" t="str"/>
+      <x:c r="K155" s="131"/>
+      <x:c r="L155" s="143"/>
+      <x:c r="M155" s="143"/>
+      <x:c r="N155" s="143"/>
+      <x:c r="O155" s="173"/>
       <x:c r="P155" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A155)&gt;0,"No",IF(E155="BECM 3204",IF(J155='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E155="BECM 3208",IF(J155='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E155="CE 3224",IF(J155='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E155="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C155,2)=1,"Yes","No"),IF(MOD(C155,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8208,28 +8241,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E156" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F156" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G156" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H156" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I156" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J156" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K156" s="131" t="str"/>
-      <x:c r="L156" s="143" t="str"/>
-      <x:c r="M156" s="143" t="str"/>
-      <x:c r="N156" s="143" t="str"/>
-      <x:c r="O156" s="173" t="str"/>
+      <x:c r="K156" s="131"/>
+      <x:c r="L156" s="143"/>
+      <x:c r="M156" s="143"/>
+      <x:c r="N156" s="143"/>
+      <x:c r="O156" s="173"/>
       <x:c r="P156" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A156)&gt;0,"No",IF(E156="BECM 3204",IF(J156='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E156="BECM 3208",IF(J156='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E156="CE 3224",IF(J156='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E156="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C156,2)=1,"Yes","No"),IF(MOD(C156,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8249,28 +8282,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E157" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F157" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G157" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H157" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I157" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J157" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K157" s="131" t="str"/>
-      <x:c r="L157" s="143" t="str"/>
-      <x:c r="M157" s="143" t="str"/>
-      <x:c r="N157" s="143" t="str"/>
-      <x:c r="O157" s="173" t="str"/>
+      <x:c r="K157" s="131"/>
+      <x:c r="L157" s="143"/>
+      <x:c r="M157" s="143"/>
+      <x:c r="N157" s="143"/>
+      <x:c r="O157" s="173"/>
       <x:c r="P157" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A157)&gt;0,"No",IF(E157="BECM 3204",IF(J157='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E157="BECM 3208",IF(J157='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E157="CE 3224",IF(J157='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E157="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C157,2)=1,"Yes","No"),IF(MOD(C157,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8301,17 +8334,15 @@
       <x:c r="H158" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I158" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I158" s="23"/>
       <x:c r="J158" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K158" s="131" t="str"/>
-      <x:c r="L158" s="143" t="str"/>
-      <x:c r="M158" s="143" t="str"/>
-      <x:c r="N158" s="143" t="str"/>
-      <x:c r="O158" s="173" t="str"/>
+      <x:c r="K158" s="131"/>
+      <x:c r="L158" s="143"/>
+      <x:c r="M158" s="143"/>
+      <x:c r="N158" s="143"/>
+      <x:c r="O158" s="173"/>
       <x:c r="P158" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A158)&gt;0,"No",IF(E158="BECM 3204",IF(J158='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E158="BECM 3208",IF(J158='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E158="CE 3224",IF(J158='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E158="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C158,2)=1,"Yes","No"),IF(MOD(C158,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -8343,16 +8374,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I159" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J159" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K159" s="131" t="str"/>
-      <x:c r="L159" s="143" t="str"/>
-      <x:c r="M159" s="143" t="str"/>
-      <x:c r="N159" s="143" t="str"/>
-      <x:c r="O159" s="173" t="str"/>
+      <x:c r="K159" s="131"/>
+      <x:c r="L159" s="143"/>
+      <x:c r="M159" s="143"/>
+      <x:c r="N159" s="143"/>
+      <x:c r="O159" s="173"/>
       <x:c r="P159" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A159)&gt;0,"No",IF(E159="BECM 3204",IF(J159='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E159="BECM 3208",IF(J159='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E159="CE 3224",IF(J159='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E159="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C159,2)=1,"Yes","No"),IF(MOD(C159,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8372,28 +8403,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E160" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F160" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G160" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H160" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I160" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J160" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K160" s="131" t="str"/>
-      <x:c r="L160" s="143" t="str"/>
-      <x:c r="M160" s="143" t="str"/>
-      <x:c r="N160" s="143" t="str"/>
-      <x:c r="O160" s="173" t="str"/>
+      <x:c r="K160" s="131"/>
+      <x:c r="L160" s="143"/>
+      <x:c r="M160" s="143"/>
+      <x:c r="N160" s="143"/>
+      <x:c r="O160" s="173"/>
       <x:c r="P160" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A160)&gt;0,"No",IF(E160="BECM 3204",IF(J160='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E160="BECM 3208",IF(J160='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E160="CE 3224",IF(J160='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E160="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C160,2)=1,"Yes","No"),IF(MOD(C160,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8413,28 +8444,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E161" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F161" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G161" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H161" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I161" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J161" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K161" s="131" t="str"/>
-      <x:c r="L161" s="143" t="str"/>
-      <x:c r="M161" s="143" t="str"/>
-      <x:c r="N161" s="143" t="str"/>
-      <x:c r="O161" s="173" t="str"/>
+      <x:c r="K161" s="131"/>
+      <x:c r="L161" s="143"/>
+      <x:c r="M161" s="143"/>
+      <x:c r="N161" s="143"/>
+      <x:c r="O161" s="173"/>
       <x:c r="P161" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A161)&gt;0,"No",IF(E161="BECM 3204",IF(J161='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E161="BECM 3208",IF(J161='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E161="CE 3224",IF(J161='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E161="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C161,2)=1,"Yes","No"),IF(MOD(C161,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8465,17 +8496,15 @@
       <x:c r="H162" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I162" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I162" s="23"/>
       <x:c r="J162" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K162" s="131" t="str"/>
-      <x:c r="L162" s="143" t="str"/>
-      <x:c r="M162" s="143" t="str"/>
-      <x:c r="N162" s="143" t="str"/>
-      <x:c r="O162" s="173" t="str"/>
+      <x:c r="K162" s="131"/>
+      <x:c r="L162" s="143"/>
+      <x:c r="M162" s="143"/>
+      <x:c r="N162" s="143"/>
+      <x:c r="O162" s="173"/>
       <x:c r="P162" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A162)&gt;0,"No",IF(E162="BECM 3204",IF(J162='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E162="BECM 3208",IF(J162='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E162="CE 3224",IF(J162='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E162="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C162,2)=1,"Yes","No"),IF(MOD(C162,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8495,28 +8524,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E163" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F163" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G163" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H163" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I163" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J163" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K163" s="131" t="str"/>
-      <x:c r="L163" s="143" t="str"/>
-      <x:c r="M163" s="143" t="str"/>
-      <x:c r="N163" s="143" t="str"/>
-      <x:c r="O163" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K163" s="131"/>
+      <x:c r="L163" s="143"/>
+      <x:c r="M163" s="143"/>
+      <x:c r="N163" s="143"/>
+      <x:c r="O163" s="173"/>
       <x:c r="P163" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A163)&gt;0,"No",IF(E163="BECM 3204",IF(J163='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E163="BECM 3208",IF(J163='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E163="CE 3224",IF(J163='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E163="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C163,2)=1,"Yes","No"),IF(MOD(C163,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8548,16 +8577,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I164" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J164" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K164" s="131" t="str"/>
-      <x:c r="L164" s="143" t="str"/>
-      <x:c r="M164" s="143" t="str"/>
-      <x:c r="N164" s="143" t="str"/>
-      <x:c r="O164" s="173" t="str"/>
+      <x:c r="K164" s="131"/>
+      <x:c r="L164" s="143"/>
+      <x:c r="M164" s="143"/>
+      <x:c r="N164" s="143"/>
+      <x:c r="O164" s="173"/>
       <x:c r="P164" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A164)&gt;0,"No",IF(E164="BECM 3204",IF(J164='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E164="BECM 3208",IF(J164='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E164="CE 3224",IF(J164='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E164="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C164,2)=1,"Yes","No"),IF(MOD(C164,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8589,16 +8618,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I165" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J165" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K165" s="131" t="str"/>
-      <x:c r="L165" s="143" t="str"/>
-      <x:c r="M165" s="143" t="str"/>
-      <x:c r="N165" s="143" t="str"/>
-      <x:c r="O165" s="173" t="str"/>
+      <x:c r="K165" s="131"/>
+      <x:c r="L165" s="143"/>
+      <x:c r="M165" s="143"/>
+      <x:c r="N165" s="143"/>
+      <x:c r="O165" s="173"/>
       <x:c r="P165" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A165)&gt;0,"No",IF(E165="BECM 3204",IF(J165='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E165="BECM 3208",IF(J165='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E165="CE 3224",IF(J165='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E165="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C165,2)=1,"Yes","No"),IF(MOD(C165,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8618,29 +8647,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E166" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F166" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G166" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H166" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I166" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I166" s="23"/>
       <x:c r="J166" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K166" s="131" t="str"/>
-      <x:c r="L166" s="143" t="str"/>
-      <x:c r="M166" s="143" t="str"/>
-      <x:c r="N166" s="143" t="str"/>
-      <x:c r="O166" s="173" t="str"/>
+      <x:c r="K166" s="131"/>
+      <x:c r="L166" s="143"/>
+      <x:c r="M166" s="143"/>
+      <x:c r="N166" s="143"/>
+      <x:c r="O166" s="173"/>
       <x:c r="P166" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A166)&gt;0,"No",IF(E166="BECM 3204",IF(J166='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E166="BECM 3208",IF(J166='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E166="CE 3224",IF(J166='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E166="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C166,2)=1,"Yes","No"),IF(MOD(C166,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -8657,26 +8686,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E167" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F167" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G167" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H167" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I167" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I167" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J167" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K167" s="131" t="str"/>
-      <x:c r="L167" s="143" t="str"/>
-      <x:c r="M167" s="143" t="str"/>
-      <x:c r="N167" s="143" t="str"/>
-      <x:c r="O167" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K167" s="131"/>
+      <x:c r="L167" s="143"/>
+      <x:c r="M167" s="143"/>
+      <x:c r="N167" s="143"/>
+      <x:c r="O167" s="173"/>
       <x:c r="P167" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A167)&gt;0,"No",IF(E167="BECM 3204",IF(J167='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E167="BECM 3208",IF(J167='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E167="CE 3224",IF(J167='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E167="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C167,2)=1,"Yes","No"),IF(MOD(C167,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8696,28 +8727,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E168" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F168" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G168" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H168" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I168" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J168" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K168" s="131" t="str"/>
-      <x:c r="L168" s="143" t="str"/>
-      <x:c r="M168" s="143" t="str"/>
-      <x:c r="N168" s="143" t="str"/>
-      <x:c r="O168" s="173" t="str"/>
+      <x:c r="K168" s="131"/>
+      <x:c r="L168" s="143"/>
+      <x:c r="M168" s="143"/>
+      <x:c r="N168" s="143"/>
+      <x:c r="O168" s="173"/>
       <x:c r="P168" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A168)&gt;0,"No",IF(E168="BECM 3204",IF(J168='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E168="BECM 3208",IF(J168='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E168="CE 3224",IF(J168='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E168="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C168,2)=1,"Yes","No"),IF(MOD(C168,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8737,28 +8768,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E169" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F169" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G169" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H169" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I169" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J169" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K169" s="131" t="str"/>
-      <x:c r="L169" s="143" t="str"/>
-      <x:c r="M169" s="143" t="str"/>
-      <x:c r="N169" s="143" t="str"/>
-      <x:c r="O169" s="173" t="str"/>
+      <x:c r="K169" s="131"/>
+      <x:c r="L169" s="143"/>
+      <x:c r="M169" s="143"/>
+      <x:c r="N169" s="143"/>
+      <x:c r="O169" s="173"/>
       <x:c r="P169" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A169)&gt;0,"No",IF(E169="BECM 3204",IF(J169='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E169="BECM 3208",IF(J169='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E169="CE 3224",IF(J169='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E169="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C169,2)=1,"Yes","No"),IF(MOD(C169,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8778,26 +8809,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E170" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F170" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G170" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H170" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I170" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I170" s="23"/>
       <x:c r="J170" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K170" s="131" t="str"/>
-      <x:c r="L170" s="143" t="str"/>
-      <x:c r="M170" s="143" t="str"/>
-      <x:c r="N170" s="143" t="str"/>
-      <x:c r="O170" s="173" t="str"/>
+      <x:c r="K170" s="131"/>
+      <x:c r="L170" s="143"/>
+      <x:c r="M170" s="143"/>
+      <x:c r="N170" s="143"/>
+      <x:c r="O170" s="173"/>
       <x:c r="P170" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A170)&gt;0,"No",IF(E170="BECM 3204",IF(J170='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E170="BECM 3208",IF(J170='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E170="CE 3224",IF(J170='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E170="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C170,2)=1,"Yes","No"),IF(MOD(C170,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8817,31 +8848,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E171" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F171" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G171" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H171" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I171" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I171" s="23"/>
       <x:c r="J171" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K171" s="131" t="str"/>
-      <x:c r="L171" s="143" t="str"/>
-      <x:c r="M171" s="143" t="str"/>
-      <x:c r="N171" s="143" t="str"/>
-      <x:c r="O171" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K171" s="131"/>
+      <x:c r="L171" s="143"/>
+      <x:c r="M171" s="143"/>
+      <x:c r="N171" s="143"/>
+      <x:c r="O171" s="173"/>
       <x:c r="P171" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A171)&gt;0,"No",IF(E171="BECM 3204",IF(J171='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E171="BECM 3208",IF(J171='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E171="CE 3224",IF(J171='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E171="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C171,2)=1,"Yes","No"),IF(MOD(C171,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -8858,28 +8887,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E172" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F172" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G172" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H172" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I172" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J172" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K172" s="131" t="str"/>
-      <x:c r="L172" s="143" t="str"/>
-      <x:c r="M172" s="143" t="str"/>
-      <x:c r="N172" s="143" t="str"/>
-      <x:c r="O172" s="173" t="str"/>
+      <x:c r="K172" s="131"/>
+      <x:c r="L172" s="143"/>
+      <x:c r="M172" s="143"/>
+      <x:c r="N172" s="143"/>
+      <x:c r="O172" s="173"/>
       <x:c r="P172" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A172)&gt;0,"No",IF(E172="BECM 3204",IF(J172='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E172="BECM 3208",IF(J172='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E172="CE 3224",IF(J172='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E172="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C172,2)=1,"Yes","No"),IF(MOD(C172,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8899,28 +8928,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E173" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F173" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G173" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H173" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I173" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J173" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K173" s="131" t="str"/>
-      <x:c r="L173" s="143" t="str"/>
-      <x:c r="M173" s="143" t="str"/>
-      <x:c r="N173" s="143" t="str"/>
-      <x:c r="O173" s="173" t="str"/>
+      <x:c r="K173" s="131"/>
+      <x:c r="L173" s="143"/>
+      <x:c r="M173" s="143"/>
+      <x:c r="N173" s="143"/>
+      <x:c r="O173" s="173"/>
       <x:c r="P173" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A173)&gt;0,"No",IF(E173="BECM 3204",IF(J173='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E173="BECM 3208",IF(J173='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E173="CE 3224",IF(J173='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E173="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C173,2)=1,"Yes","No"),IF(MOD(C173,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8952,16 +8981,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I174" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J174" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K174" s="131" t="str"/>
-      <x:c r="L174" s="143" t="str"/>
-      <x:c r="M174" s="143" t="str"/>
-      <x:c r="N174" s="143" t="str"/>
-      <x:c r="O174" s="173" t="str"/>
+      <x:c r="K174" s="131"/>
+      <x:c r="L174" s="143"/>
+      <x:c r="M174" s="143"/>
+      <x:c r="N174" s="143"/>
+      <x:c r="O174" s="173"/>
       <x:c r="P174" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A174)&gt;0,"No",IF(E174="BECM 3204",IF(J174='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E174="BECM 3208",IF(J174='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E174="CE 3224",IF(J174='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E174="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C174,2)=1,"Yes","No"),IF(MOD(C174,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -8981,28 +9010,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E175" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F175" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G175" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H175" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I175" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I175" s="23"/>
       <x:c r="J175" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K175" s="131" t="str"/>
-      <x:c r="L175" s="143" t="str"/>
-      <x:c r="M175" s="143" t="str"/>
-      <x:c r="N175" s="143" t="str"/>
-      <x:c r="O175" s="173" t="str"/>
+      <x:c r="K175" s="131"/>
+      <x:c r="L175" s="143"/>
+      <x:c r="M175" s="143"/>
+      <x:c r="N175" s="143"/>
+      <x:c r="O175" s="173"/>
       <x:c r="P175" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A175)&gt;0,"No",IF(E175="BECM 3204",IF(J175='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E175="BECM 3208",IF(J175='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E175="CE 3224",IF(J175='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E175="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C175,2)=1,"Yes","No"),IF(MOD(C175,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -9022,26 +9049,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E176" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F176" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G176" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H176" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I176" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I176" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J176" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K176" s="131" t="str"/>
-      <x:c r="L176" s="143" t="str"/>
-      <x:c r="M176" s="143" t="str"/>
-      <x:c r="N176" s="143" t="str"/>
-      <x:c r="O176" s="173" t="str"/>
+      <x:c r="K176" s="131"/>
+      <x:c r="L176" s="143"/>
+      <x:c r="M176" s="143"/>
+      <x:c r="N176" s="143"/>
+      <x:c r="O176" s="173"/>
       <x:c r="P176" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A176)&gt;0,"No",IF(E176="BECM 3204",IF(J176='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E176="BECM 3208",IF(J176='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E176="CE 3224",IF(J176='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E176="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C176,2)=1,"Yes","No"),IF(MOD(C176,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -9061,28 +9090,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E177" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F177" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G177" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H177" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I177" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J177" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K177" s="131" t="str"/>
-      <x:c r="L177" s="143" t="str"/>
-      <x:c r="M177" s="143" t="str"/>
-      <x:c r="N177" s="143" t="str"/>
-      <x:c r="O177" s="173" t="str"/>
+      <x:c r="K177" s="131"/>
+      <x:c r="L177" s="143"/>
+      <x:c r="M177" s="143"/>
+      <x:c r="N177" s="143"/>
+      <x:c r="O177" s="173"/>
       <x:c r="P177" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A177)&gt;0,"No",IF(E177="BECM 3204",IF(J177='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E177="BECM 3208",IF(J177='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E177="CE 3224",IF(J177='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E177="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C177,2)=1,"Yes","No"),IF(MOD(C177,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9102,28 +9131,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E178" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F178" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G178" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H178" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I178" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J178" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K178" s="131" t="str"/>
-      <x:c r="L178" s="143" t="str"/>
-      <x:c r="M178" s="143" t="str"/>
-      <x:c r="N178" s="143" t="str"/>
-      <x:c r="O178" s="173" t="str"/>
+      <x:c r="K178" s="131"/>
+      <x:c r="L178" s="143"/>
+      <x:c r="M178" s="143"/>
+      <x:c r="N178" s="143"/>
+      <x:c r="O178" s="173"/>
       <x:c r="P178" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A178)&gt;0,"No",IF(E178="BECM 3204",IF(J178='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E178="BECM 3208",IF(J178='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E178="CE 3224",IF(J178='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E178="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C178,2)=1,"Yes","No"),IF(MOD(C178,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9143,28 +9172,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E179" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F179" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G179" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H179" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I179" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J179" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K179" s="131" t="str"/>
-      <x:c r="L179" s="143" t="str"/>
-      <x:c r="M179" s="143" t="str"/>
-      <x:c r="N179" s="143" t="str"/>
-      <x:c r="O179" s="173" t="str"/>
+      <x:c r="K179" s="131"/>
+      <x:c r="L179" s="143"/>
+      <x:c r="M179" s="143"/>
+      <x:c r="N179" s="143"/>
+      <x:c r="O179" s="173"/>
       <x:c r="P179" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A179)&gt;0,"No",IF(E179="BECM 3204",IF(J179='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E179="BECM 3208",IF(J179='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E179="CE 3224",IF(J179='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E179="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C179,2)=1,"Yes","No"),IF(MOD(C179,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9195,17 +9224,15 @@
       <x:c r="H180" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I180" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I180" s="23"/>
       <x:c r="J180" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K180" s="131" t="str"/>
-      <x:c r="L180" s="143" t="str"/>
-      <x:c r="M180" s="143" t="str"/>
-      <x:c r="N180" s="143" t="str"/>
-      <x:c r="O180" s="173" t="str"/>
+      <x:c r="K180" s="131"/>
+      <x:c r="L180" s="143"/>
+      <x:c r="M180" s="143"/>
+      <x:c r="N180" s="143"/>
+      <x:c r="O180" s="173"/>
       <x:c r="P180" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A180)&gt;0,"No",IF(E180="BECM 3204",IF(J180='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E180="BECM 3208",IF(J180='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E180="CE 3224",IF(J180='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E180="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C180,2)=1,"Yes","No"),IF(MOD(C180,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -9237,16 +9264,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I181" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J181" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K181" s="131" t="str"/>
-      <x:c r="L181" s="143" t="str"/>
-      <x:c r="M181" s="143" t="str"/>
-      <x:c r="N181" s="143" t="str"/>
-      <x:c r="O181" s="173" t="str"/>
+      <x:c r="K181" s="131"/>
+      <x:c r="L181" s="143"/>
+      <x:c r="M181" s="143"/>
+      <x:c r="N181" s="143"/>
+      <x:c r="O181" s="173"/>
       <x:c r="P181" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A181)&gt;0,"No",IF(E181="BECM 3204",IF(J181='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E181="BECM 3208",IF(J181='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E181="CE 3224",IF(J181='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E181="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C181,2)=1,"Yes","No"),IF(MOD(C181,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9266,28 +9293,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E182" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F182" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G182" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H182" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I182" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J182" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K182" s="131" t="str"/>
-      <x:c r="L182" s="143" t="str"/>
-      <x:c r="M182" s="143" t="str"/>
-      <x:c r="N182" s="143" t="str"/>
-      <x:c r="O182" s="173" t="str"/>
+      <x:c r="K182" s="131"/>
+      <x:c r="L182" s="143"/>
+      <x:c r="M182" s="143"/>
+      <x:c r="N182" s="143"/>
+      <x:c r="O182" s="173"/>
       <x:c r="P182" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A182)&gt;0,"No",IF(E182="BECM 3204",IF(J182='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E182="BECM 3208",IF(J182='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E182="CE 3224",IF(J182='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E182="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C182,2)=1,"Yes","No"),IF(MOD(C182,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9307,28 +9334,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E183" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F183" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G183" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H183" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I183" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J183" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K183" s="131" t="str"/>
-      <x:c r="L183" s="143" t="str"/>
-      <x:c r="M183" s="143" t="str"/>
-      <x:c r="N183" s="143" t="str"/>
-      <x:c r="O183" s="173" t="str"/>
+      <x:c r="K183" s="131"/>
+      <x:c r="L183" s="143"/>
+      <x:c r="M183" s="143"/>
+      <x:c r="N183" s="143"/>
+      <x:c r="O183" s="173"/>
       <x:c r="P183" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A183)&gt;0,"No",IF(E183="BECM 3204",IF(J183='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E183="BECM 3208",IF(J183='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E183="CE 3224",IF(J183='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E183="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C183,2)=1,"Yes","No"),IF(MOD(C183,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9359,17 +9386,15 @@
       <x:c r="H184" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I184" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I184" s="23"/>
       <x:c r="J184" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K184" s="131" t="str"/>
-      <x:c r="L184" s="143" t="str"/>
-      <x:c r="M184" s="143" t="str"/>
-      <x:c r="N184" s="143" t="str"/>
-      <x:c r="O184" s="173" t="str"/>
+      <x:c r="K184" s="131"/>
+      <x:c r="L184" s="143"/>
+      <x:c r="M184" s="143"/>
+      <x:c r="N184" s="143"/>
+      <x:c r="O184" s="173"/>
       <x:c r="P184" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A184)&gt;0,"No",IF(E184="BECM 3204",IF(J184='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E184="BECM 3208",IF(J184='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E184="CE 3224",IF(J184='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E184="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C184,2)=1,"Yes","No"),IF(MOD(C184,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9389,28 +9414,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E185" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F185" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G185" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H185" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I185" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J185" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K185" s="131" t="str"/>
-      <x:c r="L185" s="143" t="str"/>
-      <x:c r="M185" s="143" t="str"/>
-      <x:c r="N185" s="143" t="str"/>
-      <x:c r="O185" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K185" s="131"/>
+      <x:c r="L185" s="143"/>
+      <x:c r="M185" s="143"/>
+      <x:c r="N185" s="143"/>
+      <x:c r="O185" s="173"/>
       <x:c r="P185" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A185)&gt;0,"No",IF(E185="BECM 3204",IF(J185='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E185="BECM 3208",IF(J185='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E185="CE 3224",IF(J185='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E185="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C185,2)=1,"Yes","No"),IF(MOD(C185,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9442,16 +9467,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I186" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J186" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K186" s="131" t="str"/>
-      <x:c r="L186" s="143" t="str"/>
-      <x:c r="M186" s="143" t="str"/>
-      <x:c r="N186" s="143" t="str"/>
-      <x:c r="O186" s="173" t="str"/>
+      <x:c r="K186" s="131"/>
+      <x:c r="L186" s="143"/>
+      <x:c r="M186" s="143"/>
+      <x:c r="N186" s="143"/>
+      <x:c r="O186" s="173"/>
       <x:c r="P186" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A186)&gt;0,"No",IF(E186="BECM 3204",IF(J186='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E186="BECM 3208",IF(J186='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E186="CE 3224",IF(J186='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E186="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C186,2)=1,"Yes","No"),IF(MOD(C186,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9483,16 +9508,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I187" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J187" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K187" s="131" t="str"/>
-      <x:c r="L187" s="143" t="str"/>
-      <x:c r="M187" s="143" t="str"/>
-      <x:c r="N187" s="143" t="str"/>
-      <x:c r="O187" s="173" t="str"/>
+      <x:c r="K187" s="131"/>
+      <x:c r="L187" s="143"/>
+      <x:c r="M187" s="143"/>
+      <x:c r="N187" s="143"/>
+      <x:c r="O187" s="173"/>
       <x:c r="P187" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A187)&gt;0,"No",IF(E187="BECM 3204",IF(J187='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E187="BECM 3208",IF(J187='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E187="CE 3224",IF(J187='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E187="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C187,2)=1,"Yes","No"),IF(MOD(C187,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9512,26 +9537,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E188" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F188" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G188" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H188" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I188" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I188" s="23"/>
       <x:c r="J188" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K188" s="131" t="str"/>
-      <x:c r="L188" s="143" t="str"/>
-      <x:c r="M188" s="143" t="str"/>
-      <x:c r="N188" s="143" t="str"/>
-      <x:c r="O188" s="173" t="str"/>
+      <x:c r="K188" s="131"/>
+      <x:c r="L188" s="143"/>
+      <x:c r="M188" s="143"/>
+      <x:c r="N188" s="143"/>
+      <x:c r="O188" s="173"/>
       <x:c r="P188" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A188)&gt;0,"No",IF(E188="BECM 3204",IF(J188='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E188="BECM 3208",IF(J188='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E188="CE 3224",IF(J188='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E188="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C188,2)=1,"Yes","No"),IF(MOD(C188,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9551,26 +9576,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E189" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F189" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G189" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H189" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I189" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I189" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J189" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K189" s="131" t="str"/>
-      <x:c r="L189" s="143" t="str"/>
-      <x:c r="M189" s="143" t="str"/>
-      <x:c r="N189" s="143" t="str"/>
-      <x:c r="O189" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K189" s="131"/>
+      <x:c r="L189" s="143"/>
+      <x:c r="M189" s="143"/>
+      <x:c r="N189" s="143"/>
+      <x:c r="O189" s="173"/>
       <x:c r="P189" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A189)&gt;0,"No",IF(E189="BECM 3204",IF(J189='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E189="BECM 3208",IF(J189='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E189="CE 3224",IF(J189='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E189="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C189,2)=1,"Yes","No"),IF(MOD(C189,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9590,28 +9617,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E190" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F190" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G190" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H190" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I190" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J190" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K190" s="131" t="str"/>
-      <x:c r="L190" s="143" t="str"/>
-      <x:c r="M190" s="143" t="str"/>
-      <x:c r="N190" s="143" t="str"/>
-      <x:c r="O190" s="173" t="str"/>
+      <x:c r="K190" s="131"/>
+      <x:c r="L190" s="143"/>
+      <x:c r="M190" s="143"/>
+      <x:c r="N190" s="143"/>
+      <x:c r="O190" s="173"/>
       <x:c r="P190" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A190)&gt;0,"No",IF(E190="BECM 3204",IF(J190='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E190="BECM 3208",IF(J190='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E190="CE 3224",IF(J190='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E190="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C190,2)=1,"Yes","No"),IF(MOD(C190,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9631,28 +9658,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E191" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F191" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G191" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H191" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I191" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J191" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K191" s="131" t="str"/>
-      <x:c r="L191" s="143" t="str"/>
-      <x:c r="M191" s="143" t="str"/>
-      <x:c r="N191" s="143" t="str"/>
-      <x:c r="O191" s="173" t="str"/>
+      <x:c r="K191" s="131"/>
+      <x:c r="L191" s="143"/>
+      <x:c r="M191" s="143"/>
+      <x:c r="N191" s="143"/>
+      <x:c r="O191" s="173"/>
       <x:c r="P191" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A191)&gt;0,"No",IF(E191="BECM 3204",IF(J191='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E191="BECM 3208",IF(J191='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E191="CE 3224",IF(J191='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E191="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C191,2)=1,"Yes","No"),IF(MOD(C191,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9672,26 +9699,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E192" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F192" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G192" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H192" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I192" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I192" s="23"/>
       <x:c r="J192" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K192" s="131" t="str"/>
-      <x:c r="L192" s="143" t="str"/>
-      <x:c r="M192" s="143" t="str"/>
-      <x:c r="N192" s="143" t="str"/>
-      <x:c r="O192" s="173" t="str"/>
+      <x:c r="K192" s="131"/>
+      <x:c r="L192" s="143"/>
+      <x:c r="M192" s="143"/>
+      <x:c r="N192" s="143"/>
+      <x:c r="O192" s="173"/>
       <x:c r="P192" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A192)&gt;0,"No",IF(E192="BECM 3204",IF(J192='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E192="BECM 3208",IF(J192='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E192="CE 3224",IF(J192='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E192="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C192,2)=1,"Yes","No"),IF(MOD(C192,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9711,31 +9738,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E193" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F193" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G193" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H193" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I193" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I193" s="23"/>
       <x:c r="J193" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K193" s="131" t="str"/>
-      <x:c r="L193" s="143" t="str"/>
-      <x:c r="M193" s="143" t="str"/>
-      <x:c r="N193" s="143" t="str"/>
-      <x:c r="O193" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K193" s="131"/>
+      <x:c r="L193" s="143"/>
+      <x:c r="M193" s="143"/>
+      <x:c r="N193" s="143"/>
+      <x:c r="O193" s="173"/>
       <x:c r="P193" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A193)&gt;0,"No",IF(E193="BECM 3204",IF(J193='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E193="BECM 3208",IF(J193='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E193="CE 3224",IF(J193='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E193="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C193,2)=1,"Yes","No"),IF(MOD(C193,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -9752,28 +9777,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E194" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F194" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G194" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H194" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I194" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J194" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K194" s="131" t="str"/>
-      <x:c r="L194" s="143" t="str"/>
-      <x:c r="M194" s="143" t="str"/>
-      <x:c r="N194" s="143" t="str"/>
-      <x:c r="O194" s="173" t="str"/>
+      <x:c r="K194" s="131"/>
+      <x:c r="L194" s="143"/>
+      <x:c r="M194" s="143"/>
+      <x:c r="N194" s="143"/>
+      <x:c r="O194" s="173"/>
       <x:c r="P194" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A194)&gt;0,"No",IF(E194="BECM 3204",IF(J194='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E194="BECM 3208",IF(J194='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E194="CE 3224",IF(J194='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E194="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C194,2)=1,"Yes","No"),IF(MOD(C194,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9793,28 +9818,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E195" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F195" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G195" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H195" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I195" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J195" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K195" s="131" t="str"/>
-      <x:c r="L195" s="143" t="str"/>
-      <x:c r="M195" s="143" t="str"/>
-      <x:c r="N195" s="143" t="str"/>
-      <x:c r="O195" s="173" t="str"/>
+      <x:c r="K195" s="131"/>
+      <x:c r="L195" s="143"/>
+      <x:c r="M195" s="143"/>
+      <x:c r="N195" s="143"/>
+      <x:c r="O195" s="173"/>
       <x:c r="P195" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A195)&gt;0,"No",IF(E195="BECM 3204",IF(J195='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E195="BECM 3208",IF(J195='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E195="CE 3224",IF(J195='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E195="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C195,2)=1,"Yes","No"),IF(MOD(C195,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9846,16 +9871,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I196" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J196" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K196" s="131" t="str"/>
-      <x:c r="L196" s="143" t="str"/>
-      <x:c r="M196" s="143" t="str"/>
-      <x:c r="N196" s="143" t="str"/>
-      <x:c r="O196" s="173" t="str"/>
+      <x:c r="K196" s="131"/>
+      <x:c r="L196" s="143"/>
+      <x:c r="M196" s="143"/>
+      <x:c r="N196" s="143"/>
+      <x:c r="O196" s="173"/>
       <x:c r="P196" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A196)&gt;0,"No",IF(E196="BECM 3204",IF(J196='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E196="BECM 3208",IF(J196='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E196="CE 3224",IF(J196='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E196="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C196,2)=1,"Yes","No"),IF(MOD(C196,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9875,28 +9900,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E197" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F197" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G197" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H197" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I197" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I197" s="23"/>
       <x:c r="J197" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K197" s="131" t="str"/>
-      <x:c r="L197" s="143" t="str"/>
-      <x:c r="M197" s="143" t="str"/>
-      <x:c r="N197" s="143" t="str"/>
-      <x:c r="O197" s="173" t="str"/>
+      <x:c r="K197" s="131"/>
+      <x:c r="L197" s="143"/>
+      <x:c r="M197" s="143"/>
+      <x:c r="N197" s="143"/>
+      <x:c r="O197" s="173"/>
       <x:c r="P197" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A197)&gt;0,"No",IF(E197="BECM 3204",IF(J197='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E197="BECM 3208",IF(J197='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E197="CE 3224",IF(J197='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E197="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C197,2)=1,"Yes","No"),IF(MOD(C197,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -9916,29 +9939,31 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E198" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F198" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G198" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H198" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I198" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I198" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J198" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K198" s="131" t="str"/>
-      <x:c r="L198" s="143" t="str"/>
-      <x:c r="M198" s="143" t="str"/>
-      <x:c r="N198" s="143" t="str"/>
-      <x:c r="O198" s="173" t="str"/>
+      <x:c r="K198" s="131"/>
+      <x:c r="L198" s="143"/>
+      <x:c r="M198" s="143"/>
+      <x:c r="N198" s="143"/>
+      <x:c r="O198" s="173"/>
       <x:c r="P198" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A198)&gt;0,"No",IF(E198="BECM 3204",IF(J198='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E198="BECM 3208",IF(J198='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E198="CE 3224",IF(J198='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E198="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C198,2)=1,"Yes","No"),IF(MOD(C198,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -9955,28 +9980,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E199" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F199" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G199" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H199" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I199" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J199" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K199" s="131" t="str"/>
-      <x:c r="L199" s="143" t="str"/>
-      <x:c r="M199" s="143" t="str"/>
-      <x:c r="N199" s="143" t="str"/>
-      <x:c r="O199" s="173" t="str"/>
+      <x:c r="K199" s="131"/>
+      <x:c r="L199" s="143"/>
+      <x:c r="M199" s="143"/>
+      <x:c r="N199" s="143"/>
+      <x:c r="O199" s="173"/>
       <x:c r="P199" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A199)&gt;0,"No",IF(E199="BECM 3204",IF(J199='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E199="BECM 3208",IF(J199='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E199="CE 3224",IF(J199='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E199="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C199,2)=1,"Yes","No"),IF(MOD(C199,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -9996,28 +10021,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E200" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F200" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G200" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H200" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I200" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J200" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K200" s="131" t="str"/>
-      <x:c r="L200" s="143" t="str"/>
-      <x:c r="M200" s="143" t="str"/>
-      <x:c r="N200" s="143" t="str"/>
-      <x:c r="O200" s="173" t="str"/>
+      <x:c r="K200" s="131"/>
+      <x:c r="L200" s="143"/>
+      <x:c r="M200" s="143"/>
+      <x:c r="N200" s="143"/>
+      <x:c r="O200" s="173"/>
       <x:c r="P200" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A200)&gt;0,"No",IF(E200="BECM 3204",IF(J200='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E200="BECM 3208",IF(J200='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E200="CE 3224",IF(J200='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E200="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C200,2)=1,"Yes","No"),IF(MOD(C200,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10037,28 +10062,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E201" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F201" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G201" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H201" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I201" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J201" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K201" s="131" t="str"/>
-      <x:c r="L201" s="143" t="str"/>
-      <x:c r="M201" s="143" t="str"/>
-      <x:c r="N201" s="143" t="str"/>
-      <x:c r="O201" s="173" t="str"/>
+      <x:c r="K201" s="131"/>
+      <x:c r="L201" s="143"/>
+      <x:c r="M201" s="143"/>
+      <x:c r="N201" s="143"/>
+      <x:c r="O201" s="173"/>
       <x:c r="P201" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A201)&gt;0,"No",IF(E201="BECM 3204",IF(J201='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E201="BECM 3208",IF(J201='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E201="CE 3224",IF(J201='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E201="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C201,2)=1,"Yes","No"),IF(MOD(C201,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10089,17 +10114,15 @@
       <x:c r="H202" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I202" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I202" s="23"/>
       <x:c r="J202" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K202" s="131" t="str"/>
-      <x:c r="L202" s="143" t="str"/>
-      <x:c r="M202" s="143" t="str"/>
-      <x:c r="N202" s="143" t="str"/>
-      <x:c r="O202" s="173" t="str"/>
+      <x:c r="K202" s="131"/>
+      <x:c r="L202" s="143"/>
+      <x:c r="M202" s="143"/>
+      <x:c r="N202" s="143"/>
+      <x:c r="O202" s="173"/>
       <x:c r="P202" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A202)&gt;0,"No",IF(E202="BECM 3204",IF(J202='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E202="BECM 3208",IF(J202='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E202="CE 3224",IF(J202='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E202="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C202,2)=1,"Yes","No"),IF(MOD(C202,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -10131,16 +10154,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I203" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J203" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K203" s="131" t="str"/>
-      <x:c r="L203" s="143" t="str"/>
-      <x:c r="M203" s="143" t="str"/>
-      <x:c r="N203" s="143" t="str"/>
-      <x:c r="O203" s="173" t="str"/>
+      <x:c r="K203" s="131"/>
+      <x:c r="L203" s="143"/>
+      <x:c r="M203" s="143"/>
+      <x:c r="N203" s="143"/>
+      <x:c r="O203" s="173"/>
       <x:c r="P203" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A203)&gt;0,"No",IF(E203="BECM 3204",IF(J203='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E203="BECM 3208",IF(J203='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E203="CE 3224",IF(J203='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E203="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C203,2)=1,"Yes","No"),IF(MOD(C203,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10160,28 +10183,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E204" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F204" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G204" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H204" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I204" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J204" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K204" s="131" t="str"/>
-      <x:c r="L204" s="143" t="str"/>
-      <x:c r="M204" s="143" t="str"/>
-      <x:c r="N204" s="143" t="str"/>
-      <x:c r="O204" s="173" t="str"/>
+      <x:c r="K204" s="131"/>
+      <x:c r="L204" s="143"/>
+      <x:c r="M204" s="143"/>
+      <x:c r="N204" s="143"/>
+      <x:c r="O204" s="173"/>
       <x:c r="P204" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A204)&gt;0,"No",IF(E204="BECM 3204",IF(J204='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E204="BECM 3208",IF(J204='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E204="CE 3224",IF(J204='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E204="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C204,2)=1,"Yes","No"),IF(MOD(C204,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10201,28 +10224,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E205" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F205" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G205" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H205" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I205" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J205" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K205" s="131" t="str"/>
-      <x:c r="L205" s="143" t="str"/>
-      <x:c r="M205" s="143" t="str"/>
-      <x:c r="N205" s="143" t="str"/>
-      <x:c r="O205" s="173" t="str"/>
+      <x:c r="K205" s="131"/>
+      <x:c r="L205" s="143"/>
+      <x:c r="M205" s="143"/>
+      <x:c r="N205" s="143"/>
+      <x:c r="O205" s="173"/>
       <x:c r="P205" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A205)&gt;0,"No",IF(E205="BECM 3204",IF(J205='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E205="BECM 3208",IF(J205='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E205="CE 3224",IF(J205='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E205="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C205,2)=1,"Yes","No"),IF(MOD(C205,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10253,17 +10276,15 @@
       <x:c r="H206" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I206" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I206" s="23"/>
       <x:c r="J206" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K206" s="131" t="str"/>
-      <x:c r="L206" s="143" t="str"/>
-      <x:c r="M206" s="143" t="str"/>
-      <x:c r="N206" s="143" t="str"/>
-      <x:c r="O206" s="173" t="str"/>
+      <x:c r="K206" s="131"/>
+      <x:c r="L206" s="143"/>
+      <x:c r="M206" s="143"/>
+      <x:c r="N206" s="143"/>
+      <x:c r="O206" s="173"/>
       <x:c r="P206" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A206)&gt;0,"No",IF(E206="BECM 3204",IF(J206='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E206="BECM 3208",IF(J206='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E206="CE 3224",IF(J206='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E206="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C206,2)=1,"Yes","No"),IF(MOD(C206,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10283,28 +10304,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E207" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F207" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G207" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H207" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I207" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J207" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K207" s="131" t="str"/>
-      <x:c r="L207" s="143" t="str"/>
-      <x:c r="M207" s="143" t="str"/>
-      <x:c r="N207" s="143" t="str"/>
-      <x:c r="O207" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K207" s="131"/>
+      <x:c r="L207" s="143"/>
+      <x:c r="M207" s="143"/>
+      <x:c r="N207" s="143"/>
+      <x:c r="O207" s="173"/>
       <x:c r="P207" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A207)&gt;0,"No",IF(E207="BECM 3204",IF(J207='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E207="BECM 3208",IF(J207='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E207="CE 3224",IF(J207='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E207="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C207,2)=1,"Yes","No"),IF(MOD(C207,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10336,16 +10357,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I208" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J208" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K208" s="131" t="str"/>
-      <x:c r="L208" s="143" t="str"/>
-      <x:c r="M208" s="143" t="str"/>
-      <x:c r="N208" s="143" t="str"/>
-      <x:c r="O208" s="173" t="str"/>
+      <x:c r="K208" s="131"/>
+      <x:c r="L208" s="143"/>
+      <x:c r="M208" s="143"/>
+      <x:c r="N208" s="143"/>
+      <x:c r="O208" s="173"/>
       <x:c r="P208" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A208)&gt;0,"No",IF(E208="BECM 3204",IF(J208='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E208="BECM 3208",IF(J208='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E208="CE 3224",IF(J208='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E208="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C208,2)=1,"Yes","No"),IF(MOD(C208,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10377,16 +10398,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I209" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J209" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K209" s="131" t="str"/>
-      <x:c r="L209" s="143" t="str"/>
-      <x:c r="M209" s="143" t="str"/>
-      <x:c r="N209" s="143" t="str"/>
-      <x:c r="O209" s="173" t="str"/>
+      <x:c r="K209" s="131"/>
+      <x:c r="L209" s="143"/>
+      <x:c r="M209" s="143"/>
+      <x:c r="N209" s="143"/>
+      <x:c r="O209" s="173"/>
       <x:c r="P209" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A209)&gt;0,"No",IF(E209="BECM 3204",IF(J209='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E209="BECM 3208",IF(J209='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E209="CE 3224",IF(J209='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E209="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C209,2)=1,"Yes","No"),IF(MOD(C209,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10406,29 +10427,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E210" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F210" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G210" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H210" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I210" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I210" s="23"/>
       <x:c r="J210" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K210" s="131" t="str"/>
-      <x:c r="L210" s="143" t="str"/>
-      <x:c r="M210" s="143" t="str"/>
-      <x:c r="N210" s="143" t="str"/>
-      <x:c r="O210" s="173" t="str"/>
+      <x:c r="K210" s="131"/>
+      <x:c r="L210" s="143"/>
+      <x:c r="M210" s="143"/>
+      <x:c r="N210" s="143"/>
+      <x:c r="O210" s="173"/>
       <x:c r="P210" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A210)&gt;0,"No",IF(E210="BECM 3204",IF(J210='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E210="BECM 3208",IF(J210='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E210="CE 3224",IF(J210='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E210="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C210,2)=1,"Yes","No"),IF(MOD(C210,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -10445,26 +10466,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E211" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F211" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G211" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H211" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I211" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I211" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J211" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K211" s="131" t="str"/>
-      <x:c r="L211" s="143" t="str"/>
-      <x:c r="M211" s="143" t="str"/>
-      <x:c r="N211" s="143" t="str"/>
-      <x:c r="O211" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K211" s="131"/>
+      <x:c r="L211" s="143"/>
+      <x:c r="M211" s="143"/>
+      <x:c r="N211" s="143"/>
+      <x:c r="O211" s="173"/>
       <x:c r="P211" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A211)&gt;0,"No",IF(E211="BECM 3204",IF(J211='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E211="BECM 3208",IF(J211='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E211="CE 3224",IF(J211='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E211="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C211,2)=1,"Yes","No"),IF(MOD(C211,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10484,28 +10507,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E212" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F212" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G212" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H212" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I212" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J212" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K212" s="131" t="str"/>
-      <x:c r="L212" s="143" t="str"/>
-      <x:c r="M212" s="143" t="str"/>
-      <x:c r="N212" s="143" t="str"/>
-      <x:c r="O212" s="173" t="str"/>
+      <x:c r="K212" s="131"/>
+      <x:c r="L212" s="143"/>
+      <x:c r="M212" s="143"/>
+      <x:c r="N212" s="143"/>
+      <x:c r="O212" s="173"/>
       <x:c r="P212" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A212)&gt;0,"No",IF(E212="BECM 3204",IF(J212='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E212="BECM 3208",IF(J212='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E212="CE 3224",IF(J212='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E212="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C212,2)=1,"Yes","No"),IF(MOD(C212,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10525,28 +10548,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E213" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F213" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G213" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H213" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I213" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J213" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K213" s="131" t="str"/>
-      <x:c r="L213" s="143" t="str"/>
-      <x:c r="M213" s="143" t="str"/>
-      <x:c r="N213" s="143" t="str"/>
-      <x:c r="O213" s="173" t="str"/>
+      <x:c r="K213" s="131"/>
+      <x:c r="L213" s="143"/>
+      <x:c r="M213" s="143"/>
+      <x:c r="N213" s="143"/>
+      <x:c r="O213" s="173"/>
       <x:c r="P213" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A213)&gt;0,"No",IF(E213="BECM 3204",IF(J213='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E213="BECM 3208",IF(J213='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E213="CE 3224",IF(J213='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E213="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C213,2)=1,"Yes","No"),IF(MOD(C213,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10566,26 +10589,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E214" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F214" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G214" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H214" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I214" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I214" s="23"/>
       <x:c r="J214" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K214" s="131" t="str"/>
-      <x:c r="L214" s="143" t="str"/>
-      <x:c r="M214" s="143" t="str"/>
-      <x:c r="N214" s="143" t="str"/>
-      <x:c r="O214" s="173" t="str"/>
+      <x:c r="K214" s="131"/>
+      <x:c r="L214" s="143"/>
+      <x:c r="M214" s="143"/>
+      <x:c r="N214" s="143"/>
+      <x:c r="O214" s="173"/>
       <x:c r="P214" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A214)&gt;0,"No",IF(E214="BECM 3204",IF(J214='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E214="BECM 3208",IF(J214='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E214="CE 3224",IF(J214='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E214="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C214,2)=1,"Yes","No"),IF(MOD(C214,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10605,31 +10628,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E215" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F215" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G215" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H215" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I215" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I215" s="23"/>
       <x:c r="J215" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K215" s="131" t="str"/>
-      <x:c r="L215" s="143" t="str"/>
-      <x:c r="M215" s="143" t="str"/>
-      <x:c r="N215" s="143" t="str"/>
-      <x:c r="O215" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K215" s="131"/>
+      <x:c r="L215" s="143"/>
+      <x:c r="M215" s="143"/>
+      <x:c r="N215" s="143"/>
+      <x:c r="O215" s="173"/>
       <x:c r="P215" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A215)&gt;0,"No",IF(E215="BECM 3204",IF(J215='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E215="BECM 3208",IF(J215='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E215="CE 3224",IF(J215='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E215="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C215,2)=1,"Yes","No"),IF(MOD(C215,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -10646,28 +10667,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E216" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F216" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G216" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H216" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I216" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J216" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K216" s="131" t="str"/>
-      <x:c r="L216" s="143" t="str"/>
-      <x:c r="M216" s="143" t="str"/>
-      <x:c r="N216" s="143" t="str"/>
-      <x:c r="O216" s="173" t="str"/>
+      <x:c r="K216" s="131"/>
+      <x:c r="L216" s="143"/>
+      <x:c r="M216" s="143"/>
+      <x:c r="N216" s="143"/>
+      <x:c r="O216" s="173"/>
       <x:c r="P216" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A216)&gt;0,"No",IF(E216="BECM 3204",IF(J216='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E216="BECM 3208",IF(J216='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E216="CE 3224",IF(J216='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E216="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C216,2)=1,"Yes","No"),IF(MOD(C216,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10687,28 +10708,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E217" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F217" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G217" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H217" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I217" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J217" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K217" s="131" t="str"/>
-      <x:c r="L217" s="143" t="str"/>
-      <x:c r="M217" s="143" t="str"/>
-      <x:c r="N217" s="143" t="str"/>
-      <x:c r="O217" s="173" t="str"/>
+      <x:c r="K217" s="131"/>
+      <x:c r="L217" s="143"/>
+      <x:c r="M217" s="143"/>
+      <x:c r="N217" s="143"/>
+      <x:c r="O217" s="173"/>
       <x:c r="P217" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A217)&gt;0,"No",IF(E217="BECM 3204",IF(J217='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E217="BECM 3208",IF(J217='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E217="CE 3224",IF(J217='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E217="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C217,2)=1,"Yes","No"),IF(MOD(C217,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10740,16 +10761,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I218" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J218" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K218" s="131" t="str"/>
-      <x:c r="L218" s="143" t="str"/>
-      <x:c r="M218" s="143" t="str"/>
-      <x:c r="N218" s="143" t="str"/>
-      <x:c r="O218" s="173" t="str"/>
+      <x:c r="K218" s="131"/>
+      <x:c r="L218" s="143"/>
+      <x:c r="M218" s="143"/>
+      <x:c r="N218" s="143"/>
+      <x:c r="O218" s="173"/>
       <x:c r="P218" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A218)&gt;0,"No",IF(E218="BECM 3204",IF(J218='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E218="BECM 3208",IF(J218='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E218="CE 3224",IF(J218='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E218="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C218,2)=1,"Yes","No"),IF(MOD(C218,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10769,28 +10790,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E219" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F219" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G219" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H219" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I219" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I219" s="23"/>
       <x:c r="J219" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K219" s="131" t="str"/>
-      <x:c r="L219" s="143" t="str"/>
-      <x:c r="M219" s="143" t="str"/>
-      <x:c r="N219" s="143" t="str"/>
-      <x:c r="O219" s="173" t="str"/>
+      <x:c r="K219" s="131"/>
+      <x:c r="L219" s="143"/>
+      <x:c r="M219" s="143"/>
+      <x:c r="N219" s="143"/>
+      <x:c r="O219" s="173"/>
       <x:c r="P219" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A219)&gt;0,"No",IF(E219="BECM 3204",IF(J219='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E219="BECM 3208",IF(J219='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E219="CE 3224",IF(J219='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E219="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C219,2)=1,"Yes","No"),IF(MOD(C219,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -10810,26 +10829,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E220" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F220" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G220" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H220" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I220" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I220" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J220" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K220" s="131" t="str"/>
-      <x:c r="L220" s="143" t="str"/>
-      <x:c r="M220" s="143" t="str"/>
-      <x:c r="N220" s="143" t="str"/>
-      <x:c r="O220" s="173" t="str"/>
+      <x:c r="K220" s="131"/>
+      <x:c r="L220" s="143"/>
+      <x:c r="M220" s="143"/>
+      <x:c r="N220" s="143"/>
+      <x:c r="O220" s="173"/>
       <x:c r="P220" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A220)&gt;0,"No",IF(E220="BECM 3204",IF(J220='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E220="BECM 3208",IF(J220='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E220="CE 3224",IF(J220='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E220="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C220,2)=1,"Yes","No"),IF(MOD(C220,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -10849,28 +10870,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E221" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F221" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G221" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H221" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I221" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J221" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K221" s="131" t="str"/>
-      <x:c r="L221" s="143" t="str"/>
-      <x:c r="M221" s="143" t="str"/>
-      <x:c r="N221" s="143" t="str"/>
-      <x:c r="O221" s="173" t="str"/>
+      <x:c r="K221" s="131"/>
+      <x:c r="L221" s="143"/>
+      <x:c r="M221" s="143"/>
+      <x:c r="N221" s="143"/>
+      <x:c r="O221" s="173"/>
       <x:c r="P221" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A221)&gt;0,"No",IF(E221="BECM 3204",IF(J221='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E221="BECM 3208",IF(J221='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E221="CE 3224",IF(J221='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E221="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C221,2)=1,"Yes","No"),IF(MOD(C221,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10890,28 +10911,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E222" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F222" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G222" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H222" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I222" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J222" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K222" s="131" t="str"/>
-      <x:c r="L222" s="143" t="str"/>
-      <x:c r="M222" s="143" t="str"/>
-      <x:c r="N222" s="143" t="str"/>
-      <x:c r="O222" s="173" t="str"/>
+      <x:c r="K222" s="131"/>
+      <x:c r="L222" s="143"/>
+      <x:c r="M222" s="143"/>
+      <x:c r="N222" s="143"/>
+      <x:c r="O222" s="173"/>
       <x:c r="P222" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A222)&gt;0,"No",IF(E222="BECM 3204",IF(J222='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E222="BECM 3208",IF(J222='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E222="CE 3224",IF(J222='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E222="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C222,2)=1,"Yes","No"),IF(MOD(C222,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10931,28 +10952,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E223" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F223" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G223" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H223" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I223" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J223" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K223" s="131" t="str"/>
-      <x:c r="L223" s="143" t="str"/>
-      <x:c r="M223" s="143" t="str"/>
-      <x:c r="N223" s="143" t="str"/>
-      <x:c r="O223" s="173" t="str"/>
+      <x:c r="K223" s="131"/>
+      <x:c r="L223" s="143"/>
+      <x:c r="M223" s="143"/>
+      <x:c r="N223" s="143"/>
+      <x:c r="O223" s="173"/>
       <x:c r="P223" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A223)&gt;0,"No",IF(E223="BECM 3204",IF(J223='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E223="BECM 3208",IF(J223='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E223="CE 3224",IF(J223='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E223="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C223,2)=1,"Yes","No"),IF(MOD(C223,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -10983,17 +11004,15 @@
       <x:c r="H224" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I224" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I224" s="23"/>
       <x:c r="J224" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K224" s="131" t="str"/>
-      <x:c r="L224" s="143" t="str"/>
-      <x:c r="M224" s="143" t="str"/>
-      <x:c r="N224" s="143" t="str"/>
-      <x:c r="O224" s="173" t="str"/>
+      <x:c r="K224" s="131"/>
+      <x:c r="L224" s="143"/>
+      <x:c r="M224" s="143"/>
+      <x:c r="N224" s="143"/>
+      <x:c r="O224" s="173"/>
       <x:c r="P224" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A224)&gt;0,"No",IF(E224="BECM 3204",IF(J224='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E224="BECM 3208",IF(J224='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E224="CE 3224",IF(J224='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E224="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C224,2)=1,"Yes","No"),IF(MOD(C224,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -11025,16 +11044,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I225" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J225" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K225" s="131" t="str"/>
-      <x:c r="L225" s="143" t="str"/>
-      <x:c r="M225" s="143" t="str"/>
-      <x:c r="N225" s="143" t="str"/>
-      <x:c r="O225" s="173" t="str"/>
+      <x:c r="K225" s="131"/>
+      <x:c r="L225" s="143"/>
+      <x:c r="M225" s="143"/>
+      <x:c r="N225" s="143"/>
+      <x:c r="O225" s="173"/>
       <x:c r="P225" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A225)&gt;0,"No",IF(E225="BECM 3204",IF(J225='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E225="BECM 3208",IF(J225='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E225="CE 3224",IF(J225='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E225="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C225,2)=1,"Yes","No"),IF(MOD(C225,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11054,28 +11073,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E226" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F226" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G226" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H226" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I226" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J226" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K226" s="131" t="str"/>
-      <x:c r="L226" s="143" t="str"/>
-      <x:c r="M226" s="143" t="str"/>
-      <x:c r="N226" s="143" t="str"/>
-      <x:c r="O226" s="173" t="str"/>
+      <x:c r="K226" s="131"/>
+      <x:c r="L226" s="143"/>
+      <x:c r="M226" s="143"/>
+      <x:c r="N226" s="143"/>
+      <x:c r="O226" s="173"/>
       <x:c r="P226" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A226)&gt;0,"No",IF(E226="BECM 3204",IF(J226='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E226="BECM 3208",IF(J226='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E226="CE 3224",IF(J226='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E226="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C226,2)=1,"Yes","No"),IF(MOD(C226,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11095,28 +11114,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E227" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F227" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G227" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H227" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I227" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J227" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K227" s="131" t="str"/>
-      <x:c r="L227" s="143" t="str"/>
-      <x:c r="M227" s="143" t="str"/>
-      <x:c r="N227" s="143" t="str"/>
-      <x:c r="O227" s="173" t="str"/>
+      <x:c r="K227" s="131"/>
+      <x:c r="L227" s="143"/>
+      <x:c r="M227" s="143"/>
+      <x:c r="N227" s="143"/>
+      <x:c r="O227" s="173"/>
       <x:c r="P227" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A227)&gt;0,"No",IF(E227="BECM 3204",IF(J227='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E227="BECM 3208",IF(J227='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E227="CE 3224",IF(J227='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E227="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C227,2)=1,"Yes","No"),IF(MOD(C227,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11147,17 +11166,15 @@
       <x:c r="H228" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I228" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I228" s="23"/>
       <x:c r="J228" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K228" s="131" t="str"/>
-      <x:c r="L228" s="143" t="str"/>
-      <x:c r="M228" s="143" t="str"/>
-      <x:c r="N228" s="143" t="str"/>
-      <x:c r="O228" s="173" t="str"/>
+      <x:c r="K228" s="131"/>
+      <x:c r="L228" s="143"/>
+      <x:c r="M228" s="143"/>
+      <x:c r="N228" s="143"/>
+      <x:c r="O228" s="173"/>
       <x:c r="P228" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A228)&gt;0,"No",IF(E228="BECM 3204",IF(J228='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E228="BECM 3208",IF(J228='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E228="CE 3224",IF(J228='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E228="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C228,2)=1,"Yes","No"),IF(MOD(C228,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11177,28 +11194,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E229" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F229" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G229" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H229" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I229" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J229" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K229" s="131" t="str"/>
-      <x:c r="L229" s="143" t="str"/>
-      <x:c r="M229" s="143" t="str"/>
-      <x:c r="N229" s="143" t="str"/>
-      <x:c r="O229" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K229" s="131"/>
+      <x:c r="L229" s="143"/>
+      <x:c r="M229" s="143"/>
+      <x:c r="N229" s="143"/>
+      <x:c r="O229" s="173"/>
       <x:c r="P229" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A229)&gt;0,"No",IF(E229="BECM 3204",IF(J229='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E229="BECM 3208",IF(J229='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E229="CE 3224",IF(J229='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E229="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C229,2)=1,"Yes","No"),IF(MOD(C229,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11230,16 +11247,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I230" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J230" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K230" s="131" t="str"/>
-      <x:c r="L230" s="143" t="str"/>
-      <x:c r="M230" s="143" t="str"/>
-      <x:c r="N230" s="143" t="str"/>
-      <x:c r="O230" s="173" t="str"/>
+      <x:c r="K230" s="131"/>
+      <x:c r="L230" s="143"/>
+      <x:c r="M230" s="143"/>
+      <x:c r="N230" s="143"/>
+      <x:c r="O230" s="173"/>
       <x:c r="P230" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A230)&gt;0,"No",IF(E230="BECM 3204",IF(J230='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E230="BECM 3208",IF(J230='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E230="CE 3224",IF(J230='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E230="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C230,2)=1,"Yes","No"),IF(MOD(C230,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11271,16 +11288,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I231" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J231" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K231" s="131" t="str"/>
-      <x:c r="L231" s="143" t="str"/>
-      <x:c r="M231" s="143" t="str"/>
-      <x:c r="N231" s="143" t="str"/>
-      <x:c r="O231" s="173" t="str"/>
+      <x:c r="K231" s="131"/>
+      <x:c r="L231" s="143"/>
+      <x:c r="M231" s="143"/>
+      <x:c r="N231" s="143"/>
+      <x:c r="O231" s="173"/>
       <x:c r="P231" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A231)&gt;0,"No",IF(E231="BECM 3204",IF(J231='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E231="BECM 3208",IF(J231='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E231="CE 3224",IF(J231='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E231="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C231,2)=1,"Yes","No"),IF(MOD(C231,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11300,26 +11317,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E232" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F232" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G232" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H232" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I232" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I232" s="23"/>
       <x:c r="J232" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K232" s="131" t="str"/>
-      <x:c r="L232" s="143" t="str"/>
-      <x:c r="M232" s="143" t="str"/>
-      <x:c r="N232" s="143" t="str"/>
-      <x:c r="O232" s="173" t="str"/>
+      <x:c r="K232" s="131"/>
+      <x:c r="L232" s="143"/>
+      <x:c r="M232" s="143"/>
+      <x:c r="N232" s="143"/>
+      <x:c r="O232" s="173"/>
       <x:c r="P232" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A232)&gt;0,"No",IF(E232="BECM 3204",IF(J232='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E232="BECM 3208",IF(J232='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E232="CE 3224",IF(J232='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E232="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C232,2)=1,"Yes","No"),IF(MOD(C232,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11339,26 +11356,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E233" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F233" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G233" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H233" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I233" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I233" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J233" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K233" s="131" t="str"/>
-      <x:c r="L233" s="143" t="str"/>
-      <x:c r="M233" s="143" t="str"/>
-      <x:c r="N233" s="143" t="str"/>
-      <x:c r="O233" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K233" s="131"/>
+      <x:c r="L233" s="143"/>
+      <x:c r="M233" s="143"/>
+      <x:c r="N233" s="143"/>
+      <x:c r="O233" s="173"/>
       <x:c r="P233" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A233)&gt;0,"No",IF(E233="BECM 3204",IF(J233='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E233="BECM 3208",IF(J233='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E233="CE 3224",IF(J233='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E233="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C233,2)=1,"Yes","No"),IF(MOD(C233,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11378,28 +11397,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E234" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F234" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G234" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H234" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I234" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J234" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K234" s="131" t="str"/>
-      <x:c r="L234" s="143" t="str"/>
-      <x:c r="M234" s="143" t="str"/>
-      <x:c r="N234" s="143" t="str"/>
-      <x:c r="O234" s="173" t="str"/>
+      <x:c r="K234" s="131"/>
+      <x:c r="L234" s="143"/>
+      <x:c r="M234" s="143"/>
+      <x:c r="N234" s="143"/>
+      <x:c r="O234" s="173"/>
       <x:c r="P234" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A234)&gt;0,"No",IF(E234="BECM 3204",IF(J234='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E234="BECM 3208",IF(J234='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E234="CE 3224",IF(J234='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E234="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C234,2)=1,"Yes","No"),IF(MOD(C234,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11419,28 +11438,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E235" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F235" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G235" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H235" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I235" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J235" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K235" s="131" t="str"/>
-      <x:c r="L235" s="143" t="str"/>
-      <x:c r="M235" s="143" t="str"/>
-      <x:c r="N235" s="143" t="str"/>
-      <x:c r="O235" s="173" t="str"/>
+      <x:c r="K235" s="131"/>
+      <x:c r="L235" s="143"/>
+      <x:c r="M235" s="143"/>
+      <x:c r="N235" s="143"/>
+      <x:c r="O235" s="173"/>
       <x:c r="P235" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A235)&gt;0,"No",IF(E235="BECM 3204",IF(J235='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E235="BECM 3208",IF(J235='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E235="CE 3224",IF(J235='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E235="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C235,2)=1,"Yes","No"),IF(MOD(C235,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11460,26 +11479,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E236" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F236" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G236" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H236" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I236" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I236" s="23"/>
       <x:c r="J236" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K236" s="131" t="str"/>
-      <x:c r="L236" s="143" t="str"/>
-      <x:c r="M236" s="143" t="str"/>
-      <x:c r="N236" s="143" t="str"/>
-      <x:c r="O236" s="173" t="str"/>
+      <x:c r="K236" s="131"/>
+      <x:c r="L236" s="143"/>
+      <x:c r="M236" s="143"/>
+      <x:c r="N236" s="143"/>
+      <x:c r="O236" s="173"/>
       <x:c r="P236" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A236)&gt;0,"No",IF(E236="BECM 3204",IF(J236='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E236="BECM 3208",IF(J236='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E236="CE 3224",IF(J236='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E236="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C236,2)=1,"Yes","No"),IF(MOD(C236,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11499,31 +11518,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E237" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F237" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G237" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H237" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I237" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I237" s="23"/>
       <x:c r="J237" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K237" s="131" t="str"/>
-      <x:c r="L237" s="143" t="str"/>
-      <x:c r="M237" s="143" t="str"/>
-      <x:c r="N237" s="143" t="str"/>
-      <x:c r="O237" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K237" s="131"/>
+      <x:c r="L237" s="143"/>
+      <x:c r="M237" s="143"/>
+      <x:c r="N237" s="143"/>
+      <x:c r="O237" s="173"/>
       <x:c r="P237" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A237)&gt;0,"No",IF(E237="BECM 3204",IF(J237='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E237="BECM 3208",IF(J237='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E237="CE 3224",IF(J237='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E237="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C237,2)=1,"Yes","No"),IF(MOD(C237,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -11540,28 +11557,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E238" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F238" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G238" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H238" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I238" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J238" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K238" s="131" t="str"/>
-      <x:c r="L238" s="143" t="str"/>
-      <x:c r="M238" s="143" t="str"/>
-      <x:c r="N238" s="143" t="str"/>
-      <x:c r="O238" s="173" t="str"/>
+      <x:c r="K238" s="131"/>
+      <x:c r="L238" s="143"/>
+      <x:c r="M238" s="143"/>
+      <x:c r="N238" s="143"/>
+      <x:c r="O238" s="173"/>
       <x:c r="P238" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A238)&gt;0,"No",IF(E238="BECM 3204",IF(J238='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E238="BECM 3208",IF(J238='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E238="CE 3224",IF(J238='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E238="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C238,2)=1,"Yes","No"),IF(MOD(C238,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11581,28 +11598,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E239" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F239" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G239" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H239" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I239" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J239" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K239" s="131" t="str"/>
-      <x:c r="L239" s="143" t="str"/>
-      <x:c r="M239" s="143" t="str"/>
-      <x:c r="N239" s="143" t="str"/>
-      <x:c r="O239" s="173" t="str"/>
+      <x:c r="K239" s="131"/>
+      <x:c r="L239" s="143"/>
+      <x:c r="M239" s="143"/>
+      <x:c r="N239" s="143"/>
+      <x:c r="O239" s="173"/>
       <x:c r="P239" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A239)&gt;0,"No",IF(E239="BECM 3204",IF(J239='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E239="BECM 3208",IF(J239='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E239="CE 3224",IF(J239='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E239="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C239,2)=1,"Yes","No"),IF(MOD(C239,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11634,16 +11651,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I240" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J240" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K240" s="131" t="str"/>
-      <x:c r="L240" s="143" t="str"/>
-      <x:c r="M240" s="143" t="str"/>
-      <x:c r="N240" s="143" t="str"/>
-      <x:c r="O240" s="173" t="str"/>
+      <x:c r="K240" s="131"/>
+      <x:c r="L240" s="143"/>
+      <x:c r="M240" s="143"/>
+      <x:c r="N240" s="143"/>
+      <x:c r="O240" s="173"/>
       <x:c r="P240" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A240)&gt;0,"No",IF(E240="BECM 3204",IF(J240='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E240="BECM 3208",IF(J240='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E240="CE 3224",IF(J240='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E240="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C240,2)=1,"Yes","No"),IF(MOD(C240,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11663,28 +11680,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E241" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F241" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G241" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H241" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I241" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I241" s="23"/>
       <x:c r="J241" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K241" s="131" t="str"/>
-      <x:c r="L241" s="143" t="str"/>
-      <x:c r="M241" s="143" t="str"/>
-      <x:c r="N241" s="143" t="str"/>
-      <x:c r="O241" s="173" t="str"/>
+      <x:c r="K241" s="131"/>
+      <x:c r="L241" s="143"/>
+      <x:c r="M241" s="143"/>
+      <x:c r="N241" s="143"/>
+      <x:c r="O241" s="173"/>
       <x:c r="P241" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A241)&gt;0,"No",IF(E241="BECM 3204",IF(J241='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E241="BECM 3208",IF(J241='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E241="CE 3224",IF(J241='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E241="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C241,2)=1,"Yes","No"),IF(MOD(C241,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -11704,29 +11719,31 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E242" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F242" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G242" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H242" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I242" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I242" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J242" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K242" s="131" t="str"/>
-      <x:c r="L242" s="143" t="str"/>
-      <x:c r="M242" s="143" t="str"/>
-      <x:c r="N242" s="143" t="str"/>
-      <x:c r="O242" s="173" t="str"/>
+      <x:c r="K242" s="131"/>
+      <x:c r="L242" s="143"/>
+      <x:c r="M242" s="143"/>
+      <x:c r="N242" s="143"/>
+      <x:c r="O242" s="173"/>
       <x:c r="P242" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A242)&gt;0,"No",IF(E242="BECM 3204",IF(J242='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E242="BECM 3208",IF(J242='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E242="CE 3224",IF(J242='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E242="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C242,2)=1,"Yes","No"),IF(MOD(C242,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -11743,28 +11760,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E243" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F243" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G243" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H243" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I243" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J243" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K243" s="131" t="str"/>
-      <x:c r="L243" s="143" t="str"/>
-      <x:c r="M243" s="143" t="str"/>
-      <x:c r="N243" s="143" t="str"/>
-      <x:c r="O243" s="173" t="str"/>
+      <x:c r="K243" s="131"/>
+      <x:c r="L243" s="143"/>
+      <x:c r="M243" s="143"/>
+      <x:c r="N243" s="143"/>
+      <x:c r="O243" s="173"/>
       <x:c r="P243" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A243)&gt;0,"No",IF(E243="BECM 3204",IF(J243='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E243="BECM 3208",IF(J243='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E243="CE 3224",IF(J243='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E243="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C243,2)=1,"Yes","No"),IF(MOD(C243,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11784,28 +11801,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E244" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F244" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G244" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H244" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I244" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J244" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K244" s="131" t="str"/>
-      <x:c r="L244" s="143" t="str"/>
-      <x:c r="M244" s="143" t="str"/>
-      <x:c r="N244" s="143" t="str"/>
-      <x:c r="O244" s="173" t="str"/>
+      <x:c r="K244" s="131"/>
+      <x:c r="L244" s="143"/>
+      <x:c r="M244" s="143"/>
+      <x:c r="N244" s="143"/>
+      <x:c r="O244" s="173"/>
       <x:c r="P244" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A244)&gt;0,"No",IF(E244="BECM 3204",IF(J244='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E244="BECM 3208",IF(J244='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E244="CE 3224",IF(J244='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E244="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C244,2)=1,"Yes","No"),IF(MOD(C244,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11825,28 +11842,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E245" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F245" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G245" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H245" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I245" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J245" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K245" s="131" t="str"/>
-      <x:c r="L245" s="143" t="str"/>
-      <x:c r="M245" s="143" t="str"/>
-      <x:c r="N245" s="143" t="str"/>
-      <x:c r="O245" s="173" t="str"/>
+      <x:c r="K245" s="131"/>
+      <x:c r="L245" s="143"/>
+      <x:c r="M245" s="143"/>
+      <x:c r="N245" s="143"/>
+      <x:c r="O245" s="173"/>
       <x:c r="P245" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A245)&gt;0,"No",IF(E245="BECM 3204",IF(J245='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E245="BECM 3208",IF(J245='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E245="CE 3224",IF(J245='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E245="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C245,2)=1,"Yes","No"),IF(MOD(C245,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11877,17 +11894,15 @@
       <x:c r="H246" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I246" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I246" s="23"/>
       <x:c r="J246" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K246" s="131" t="str"/>
-      <x:c r="L246" s="143" t="str"/>
-      <x:c r="M246" s="143" t="str"/>
-      <x:c r="N246" s="143" t="str"/>
-      <x:c r="O246" s="173" t="str"/>
+      <x:c r="K246" s="131"/>
+      <x:c r="L246" s="143"/>
+      <x:c r="M246" s="143"/>
+      <x:c r="N246" s="143"/>
+      <x:c r="O246" s="173"/>
       <x:c r="P246" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A246)&gt;0,"No",IF(E246="BECM 3204",IF(J246='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E246="BECM 3208",IF(J246='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E246="CE 3224",IF(J246='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E246="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C246,2)=1,"Yes","No"),IF(MOD(C246,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -11919,16 +11934,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I247" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J247" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K247" s="131" t="str"/>
-      <x:c r="L247" s="143" t="str"/>
-      <x:c r="M247" s="143" t="str"/>
-      <x:c r="N247" s="143" t="str"/>
-      <x:c r="O247" s="173" t="str"/>
+      <x:c r="K247" s="131"/>
+      <x:c r="L247" s="143"/>
+      <x:c r="M247" s="143"/>
+      <x:c r="N247" s="143"/>
+      <x:c r="O247" s="173"/>
       <x:c r="P247" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A247)&gt;0,"No",IF(E247="BECM 3204",IF(J247='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E247="BECM 3208",IF(J247='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E247="CE 3224",IF(J247='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E247="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C247,2)=1,"Yes","No"),IF(MOD(C247,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11948,28 +11963,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E248" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F248" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G248" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H248" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I248" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J248" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K248" s="131" t="str"/>
-      <x:c r="L248" s="143" t="str"/>
-      <x:c r="M248" s="143" t="str"/>
-      <x:c r="N248" s="143" t="str"/>
-      <x:c r="O248" s="173" t="str"/>
+      <x:c r="K248" s="131"/>
+      <x:c r="L248" s="143"/>
+      <x:c r="M248" s="143"/>
+      <x:c r="N248" s="143"/>
+      <x:c r="O248" s="173"/>
       <x:c r="P248" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A248)&gt;0,"No",IF(E248="BECM 3204",IF(J248='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E248="BECM 3208",IF(J248='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E248="CE 3224",IF(J248='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E248="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C248,2)=1,"Yes","No"),IF(MOD(C248,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -11989,28 +12004,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E249" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F249" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G249" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H249" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I249" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J249" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K249" s="131" t="str"/>
-      <x:c r="L249" s="143" t="str"/>
-      <x:c r="M249" s="143" t="str"/>
-      <x:c r="N249" s="143" t="str"/>
-      <x:c r="O249" s="173" t="str"/>
+      <x:c r="K249" s="131"/>
+      <x:c r="L249" s="143"/>
+      <x:c r="M249" s="143"/>
+      <x:c r="N249" s="143"/>
+      <x:c r="O249" s="173"/>
       <x:c r="P249" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A249)&gt;0,"No",IF(E249="BECM 3204",IF(J249='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E249="BECM 3208",IF(J249='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E249="CE 3224",IF(J249='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E249="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C249,2)=1,"Yes","No"),IF(MOD(C249,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12041,17 +12056,15 @@
       <x:c r="H250" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I250" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I250" s="23"/>
       <x:c r="J250" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K250" s="131" t="str"/>
-      <x:c r="L250" s="143" t="str"/>
-      <x:c r="M250" s="143" t="str"/>
-      <x:c r="N250" s="143" t="str"/>
-      <x:c r="O250" s="173" t="str"/>
+      <x:c r="K250" s="131"/>
+      <x:c r="L250" s="143"/>
+      <x:c r="M250" s="143"/>
+      <x:c r="N250" s="143"/>
+      <x:c r="O250" s="173"/>
       <x:c r="P250" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A250)&gt;0,"No",IF(E250="BECM 3204",IF(J250='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E250="BECM 3208",IF(J250='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E250="CE 3224",IF(J250='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E250="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C250,2)=1,"Yes","No"),IF(MOD(C250,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12071,28 +12084,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E251" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F251" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G251" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H251" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I251" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J251" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K251" s="131" t="str"/>
-      <x:c r="L251" s="143" t="str"/>
-      <x:c r="M251" s="143" t="str"/>
-      <x:c r="N251" s="143" t="str"/>
-      <x:c r="O251" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K251" s="131"/>
+      <x:c r="L251" s="143"/>
+      <x:c r="M251" s="143"/>
+      <x:c r="N251" s="143"/>
+      <x:c r="O251" s="173"/>
       <x:c r="P251" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A251)&gt;0,"No",IF(E251="BECM 3204",IF(J251='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E251="BECM 3208",IF(J251='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E251="CE 3224",IF(J251='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E251="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C251,2)=1,"Yes","No"),IF(MOD(C251,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12124,16 +12137,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I252" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J252" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K252" s="131" t="str"/>
-      <x:c r="L252" s="143" t="str"/>
-      <x:c r="M252" s="143" t="str"/>
-      <x:c r="N252" s="143" t="str"/>
-      <x:c r="O252" s="173" t="str"/>
+      <x:c r="K252" s="131"/>
+      <x:c r="L252" s="143"/>
+      <x:c r="M252" s="143"/>
+      <x:c r="N252" s="143"/>
+      <x:c r="O252" s="173"/>
       <x:c r="P252" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A252)&gt;0,"No",IF(E252="BECM 3204",IF(J252='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E252="BECM 3208",IF(J252='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E252="CE 3224",IF(J252='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E252="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C252,2)=1,"Yes","No"),IF(MOD(C252,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12165,16 +12178,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I253" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J253" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K253" s="131" t="str"/>
-      <x:c r="L253" s="143" t="str"/>
-      <x:c r="M253" s="143" t="str"/>
-      <x:c r="N253" s="143" t="str"/>
-      <x:c r="O253" s="173" t="str"/>
+      <x:c r="K253" s="131"/>
+      <x:c r="L253" s="143"/>
+      <x:c r="M253" s="143"/>
+      <x:c r="N253" s="143"/>
+      <x:c r="O253" s="173"/>
       <x:c r="P253" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A253)&gt;0,"No",IF(E253="BECM 3204",IF(J253='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E253="BECM 3208",IF(J253='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E253="CE 3224",IF(J253='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E253="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C253,2)=1,"Yes","No"),IF(MOD(C253,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12194,29 +12207,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E254" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F254" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G254" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H254" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I254" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I254" s="23"/>
       <x:c r="J254" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K254" s="131" t="str"/>
-      <x:c r="L254" s="143" t="str"/>
-      <x:c r="M254" s="143" t="str"/>
-      <x:c r="N254" s="143" t="str"/>
-      <x:c r="O254" s="173" t="str"/>
+      <x:c r="K254" s="131"/>
+      <x:c r="L254" s="143"/>
+      <x:c r="M254" s="143"/>
+      <x:c r="N254" s="143"/>
+      <x:c r="O254" s="173"/>
       <x:c r="P254" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A254)&gt;0,"No",IF(E254="BECM 3204",IF(J254='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E254="BECM 3208",IF(J254='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E254="CE 3224",IF(J254='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E254="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C254,2)=1,"Yes","No"),IF(MOD(C254,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -12233,26 +12246,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E255" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F255" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G255" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H255" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I255" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I255" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J255" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K255" s="131" t="str"/>
-      <x:c r="L255" s="143" t="str"/>
-      <x:c r="M255" s="143" t="str"/>
-      <x:c r="N255" s="143" t="str"/>
-      <x:c r="O255" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K255" s="131"/>
+      <x:c r="L255" s="143"/>
+      <x:c r="M255" s="143"/>
+      <x:c r="N255" s="143"/>
+      <x:c r="O255" s="173"/>
       <x:c r="P255" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A255)&gt;0,"No",IF(E255="BECM 3204",IF(J255='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E255="BECM 3208",IF(J255='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E255="CE 3224",IF(J255='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E255="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C255,2)=1,"Yes","No"),IF(MOD(C255,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12272,28 +12287,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E256" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F256" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G256" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H256" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I256" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J256" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K256" s="131" t="str"/>
-      <x:c r="L256" s="143" t="str"/>
-      <x:c r="M256" s="143" t="str"/>
-      <x:c r="N256" s="143" t="str"/>
-      <x:c r="O256" s="173" t="str"/>
+      <x:c r="K256" s="131"/>
+      <x:c r="L256" s="143"/>
+      <x:c r="M256" s="143"/>
+      <x:c r="N256" s="143"/>
+      <x:c r="O256" s="173"/>
       <x:c r="P256" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A256)&gt;0,"No",IF(E256="BECM 3204",IF(J256='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E256="BECM 3208",IF(J256='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E256="CE 3224",IF(J256='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E256="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C256,2)=1,"Yes","No"),IF(MOD(C256,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12313,28 +12328,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E257" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F257" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G257" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H257" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I257" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J257" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K257" s="131" t="str"/>
-      <x:c r="L257" s="143" t="str"/>
-      <x:c r="M257" s="143" t="str"/>
-      <x:c r="N257" s="143" t="str"/>
-      <x:c r="O257" s="173" t="str"/>
+      <x:c r="K257" s="131"/>
+      <x:c r="L257" s="143"/>
+      <x:c r="M257" s="143"/>
+      <x:c r="N257" s="143"/>
+      <x:c r="O257" s="173"/>
       <x:c r="P257" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A257)&gt;0,"No",IF(E257="BECM 3204",IF(J257='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E257="BECM 3208",IF(J257='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E257="CE 3224",IF(J257='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E257="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C257,2)=1,"Yes","No"),IF(MOD(C257,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12354,26 +12369,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E258" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F258" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G258" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H258" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I258" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I258" s="23"/>
       <x:c r="J258" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K258" s="131" t="str"/>
-      <x:c r="L258" s="143" t="str"/>
-      <x:c r="M258" s="143" t="str"/>
-      <x:c r="N258" s="143" t="str"/>
-      <x:c r="O258" s="173" t="str"/>
+      <x:c r="K258" s="131"/>
+      <x:c r="L258" s="143"/>
+      <x:c r="M258" s="143"/>
+      <x:c r="N258" s="143"/>
+      <x:c r="O258" s="173"/>
       <x:c r="P258" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A258)&gt;0,"No",IF(E258="BECM 3204",IF(J258='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E258="BECM 3208",IF(J258='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E258="CE 3224",IF(J258='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E258="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C258,2)=1,"Yes","No"),IF(MOD(C258,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12393,31 +12408,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E259" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F259" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G259" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H259" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I259" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I259" s="23"/>
       <x:c r="J259" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K259" s="131" t="str"/>
-      <x:c r="L259" s="143" t="str"/>
-      <x:c r="M259" s="143" t="str"/>
-      <x:c r="N259" s="143" t="str"/>
-      <x:c r="O259" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K259" s="131"/>
+      <x:c r="L259" s="143"/>
+      <x:c r="M259" s="143"/>
+      <x:c r="N259" s="143"/>
+      <x:c r="O259" s="173"/>
       <x:c r="P259" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A259)&gt;0,"No",IF(E259="BECM 3204",IF(J259='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E259="BECM 3208",IF(J259='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E259="CE 3224",IF(J259='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E259="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C259,2)=1,"Yes","No"),IF(MOD(C259,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -12434,28 +12447,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E260" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F260" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G260" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H260" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I260" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J260" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K260" s="131" t="str"/>
-      <x:c r="L260" s="143" t="str"/>
-      <x:c r="M260" s="143" t="str"/>
-      <x:c r="N260" s="143" t="str"/>
-      <x:c r="O260" s="173" t="str"/>
+      <x:c r="K260" s="131"/>
+      <x:c r="L260" s="143"/>
+      <x:c r="M260" s="143"/>
+      <x:c r="N260" s="143"/>
+      <x:c r="O260" s="173"/>
       <x:c r="P260" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A260)&gt;0,"No",IF(E260="BECM 3204",IF(J260='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E260="BECM 3208",IF(J260='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E260="CE 3224",IF(J260='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E260="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C260,2)=1,"Yes","No"),IF(MOD(C260,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12475,28 +12488,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E261" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F261" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G261" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H261" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I261" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J261" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K261" s="131" t="str"/>
-      <x:c r="L261" s="143" t="str"/>
-      <x:c r="M261" s="143" t="str"/>
-      <x:c r="N261" s="143" t="str"/>
-      <x:c r="O261" s="173" t="str"/>
+      <x:c r="K261" s="131"/>
+      <x:c r="L261" s="143"/>
+      <x:c r="M261" s="143"/>
+      <x:c r="N261" s="143"/>
+      <x:c r="O261" s="173"/>
       <x:c r="P261" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A261)&gt;0,"No",IF(E261="BECM 3204",IF(J261='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E261="BECM 3208",IF(J261='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E261="CE 3224",IF(J261='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E261="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C261,2)=1,"Yes","No"),IF(MOD(C261,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12528,16 +12541,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I262" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J262" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K262" s="131" t="str"/>
-      <x:c r="L262" s="143" t="str"/>
-      <x:c r="M262" s="143" t="str"/>
-      <x:c r="N262" s="143" t="str"/>
-      <x:c r="O262" s="173" t="str"/>
+      <x:c r="K262" s="131"/>
+      <x:c r="L262" s="143"/>
+      <x:c r="M262" s="143"/>
+      <x:c r="N262" s="143"/>
+      <x:c r="O262" s="173"/>
       <x:c r="P262" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A262)&gt;0,"No",IF(E262="BECM 3204",IF(J262='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E262="BECM 3208",IF(J262='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E262="CE 3224",IF(J262='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E262="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C262,2)=1,"Yes","No"),IF(MOD(C262,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12557,28 +12570,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E263" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F263" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G263" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H263" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I263" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I263" s="23"/>
       <x:c r="J263" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K263" s="131" t="str"/>
-      <x:c r="L263" s="143" t="str"/>
-      <x:c r="M263" s="143" t="str"/>
-      <x:c r="N263" s="143" t="str"/>
-      <x:c r="O263" s="173" t="str"/>
+      <x:c r="K263" s="131"/>
+      <x:c r="L263" s="143"/>
+      <x:c r="M263" s="143"/>
+      <x:c r="N263" s="143"/>
+      <x:c r="O263" s="173"/>
       <x:c r="P263" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A263)&gt;0,"No",IF(E263="BECM 3204",IF(J263='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E263="BECM 3208",IF(J263='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E263="CE 3224",IF(J263='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E263="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C263,2)=1,"Yes","No"),IF(MOD(C263,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -12598,26 +12609,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E264" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F264" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G264" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H264" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I264" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I264" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J264" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K264" s="131" t="str"/>
-      <x:c r="L264" s="143" t="str"/>
-      <x:c r="M264" s="143" t="str"/>
-      <x:c r="N264" s="143" t="str"/>
-      <x:c r="O264" s="173" t="str"/>
+      <x:c r="K264" s="131"/>
+      <x:c r="L264" s="143"/>
+      <x:c r="M264" s="143"/>
+      <x:c r="N264" s="143"/>
+      <x:c r="O264" s="173"/>
       <x:c r="P264" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A264)&gt;0,"No",IF(E264="BECM 3204",IF(J264='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E264="BECM 3208",IF(J264='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E264="CE 3224",IF(J264='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E264="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C264,2)=1,"Yes","No"),IF(MOD(C264,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -12637,28 +12650,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E265" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F265" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G265" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H265" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I265" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J265" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K265" s="131" t="str"/>
-      <x:c r="L265" s="143" t="str"/>
-      <x:c r="M265" s="143" t="str"/>
-      <x:c r="N265" s="143" t="str"/>
-      <x:c r="O265" s="173" t="str"/>
+      <x:c r="K265" s="131"/>
+      <x:c r="L265" s="143"/>
+      <x:c r="M265" s="143"/>
+      <x:c r="N265" s="143"/>
+      <x:c r="O265" s="173"/>
       <x:c r="P265" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A265)&gt;0,"No",IF(E265="BECM 3204",IF(J265='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E265="BECM 3208",IF(J265='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E265="CE 3224",IF(J265='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E265="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C265,2)=1,"Yes","No"),IF(MOD(C265,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12678,28 +12691,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E266" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F266" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G266" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H266" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I266" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J266" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K266" s="131" t="str"/>
-      <x:c r="L266" s="143" t="str"/>
-      <x:c r="M266" s="143" t="str"/>
-      <x:c r="N266" s="143" t="str"/>
-      <x:c r="O266" s="173" t="str"/>
+      <x:c r="K266" s="131"/>
+      <x:c r="L266" s="143"/>
+      <x:c r="M266" s="143"/>
+      <x:c r="N266" s="143"/>
+      <x:c r="O266" s="173"/>
       <x:c r="P266" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A266)&gt;0,"No",IF(E266="BECM 3204",IF(J266='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E266="BECM 3208",IF(J266='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E266="CE 3224",IF(J266='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E266="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C266,2)=1,"Yes","No"),IF(MOD(C266,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12719,28 +12732,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E267" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F267" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G267" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H267" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I267" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J267" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K267" s="131" t="str"/>
-      <x:c r="L267" s="143" t="str"/>
-      <x:c r="M267" s="143" t="str"/>
-      <x:c r="N267" s="143" t="str"/>
-      <x:c r="O267" s="173" t="str"/>
+      <x:c r="K267" s="131"/>
+      <x:c r="L267" s="143"/>
+      <x:c r="M267" s="143"/>
+      <x:c r="N267" s="143"/>
+      <x:c r="O267" s="173"/>
       <x:c r="P267" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A267)&gt;0,"No",IF(E267="BECM 3204",IF(J267='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E267="BECM 3208",IF(J267='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E267="CE 3224",IF(J267='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E267="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C267,2)=1,"Yes","No"),IF(MOD(C267,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12771,17 +12784,15 @@
       <x:c r="H268" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I268" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I268" s="23"/>
       <x:c r="J268" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K268" s="131" t="str"/>
-      <x:c r="L268" s="143" t="str"/>
-      <x:c r="M268" s="143" t="str"/>
-      <x:c r="N268" s="143" t="str"/>
-      <x:c r="O268" s="173" t="str"/>
+      <x:c r="K268" s="131"/>
+      <x:c r="L268" s="143"/>
+      <x:c r="M268" s="143"/>
+      <x:c r="N268" s="143"/>
+      <x:c r="O268" s="173"/>
       <x:c r="P268" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A268)&gt;0,"No",IF(E268="BECM 3204",IF(J268='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E268="BECM 3208",IF(J268='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E268="CE 3224",IF(J268='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E268="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C268,2)=1,"Yes","No"),IF(MOD(C268,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -12813,16 +12824,16 @@
         <x:v>HRS</x:v>
       </x:c>
       <x:c r="I269" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J269" s="23" t="str">
         <x:v>SUN P4</x:v>
       </x:c>
-      <x:c r="K269" s="131" t="str"/>
-      <x:c r="L269" s="143" t="str"/>
-      <x:c r="M269" s="143" t="str"/>
-      <x:c r="N269" s="143" t="str"/>
-      <x:c r="O269" s="173" t="str"/>
+      <x:c r="K269" s="131"/>
+      <x:c r="L269" s="143"/>
+      <x:c r="M269" s="143"/>
+      <x:c r="N269" s="143"/>
+      <x:c r="O269" s="173"/>
       <x:c r="P269" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A269)&gt;0,"No",IF(E269="BECM 3204",IF(J269='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E269="BECM 3208",IF(J269='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E269="CE 3224",IF(J269='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E269="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C269,2)=1,"Yes","No"),IF(MOD(C269,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12842,28 +12853,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E270" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F270" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G270" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H270" s="23" t="str">
-        <x:v>MSA</x:v>
+        <x:v>MKI/ATB</x:v>
       </x:c>
       <x:c r="I270" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J270" s="23" t="str">
         <x:v>SUN P5</x:v>
       </x:c>
-      <x:c r="K270" s="131" t="str"/>
-      <x:c r="L270" s="143" t="str"/>
-      <x:c r="M270" s="143" t="str"/>
-      <x:c r="N270" s="143" t="str"/>
-      <x:c r="O270" s="173" t="str"/>
+      <x:c r="K270" s="131"/>
+      <x:c r="L270" s="143"/>
+      <x:c r="M270" s="143"/>
+      <x:c r="N270" s="143"/>
+      <x:c r="O270" s="173"/>
       <x:c r="P270" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A270)&gt;0,"No",IF(E270="BECM 3204",IF(J270='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E270="BECM 3208",IF(J270='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E270="CE 3224",IF(J270='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E270="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C270,2)=1,"Yes","No"),IF(MOD(C270,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12883,28 +12894,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E271" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F271" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G271" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H271" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>MHI/MSA</x:v>
       </x:c>
       <x:c r="I271" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J271" s="23" t="str">
         <x:v>SUN P6</x:v>
       </x:c>
-      <x:c r="K271" s="131" t="str"/>
-      <x:c r="L271" s="143" t="str"/>
-      <x:c r="M271" s="143" t="str"/>
-      <x:c r="N271" s="143" t="str"/>
-      <x:c r="O271" s="173" t="str"/>
+      <x:c r="K271" s="131"/>
+      <x:c r="L271" s="143"/>
+      <x:c r="M271" s="143"/>
+      <x:c r="N271" s="143"/>
+      <x:c r="O271" s="173"/>
       <x:c r="P271" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A271)&gt;0,"No",IF(E271="BECM 3204",IF(J271='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E271="BECM 3208",IF(J271='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E271="CE 3224",IF(J271='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E271="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C271,2)=1,"Yes","No"),IF(MOD(C271,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12935,17 +12946,15 @@
       <x:c r="H272" s="23" t="str">
         <x:v>HRS/MR</x:v>
       </x:c>
-      <x:c r="I272" s="23" t="str">
-        <x:v>404</x:v>
-      </x:c>
+      <x:c r="I272" s="23"/>
       <x:c r="J272" s="23" t="str">
         <x:v>Sun PM</x:v>
       </x:c>
-      <x:c r="K272" s="131" t="str"/>
-      <x:c r="L272" s="143" t="str"/>
-      <x:c r="M272" s="143" t="str"/>
-      <x:c r="N272" s="143" t="str"/>
-      <x:c r="O272" s="173" t="str"/>
+      <x:c r="K272" s="131"/>
+      <x:c r="L272" s="143"/>
+      <x:c r="M272" s="143"/>
+      <x:c r="N272" s="143"/>
+      <x:c r="O272" s="173"/>
       <x:c r="P272" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A272)&gt;0,"No",IF(E272="BECM 3204",IF(J272='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E272="BECM 3208",IF(J272='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E272="CE 3224",IF(J272='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E272="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C272,2)=1,"Yes","No"),IF(MOD(C272,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -12965,28 +12974,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E273" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F273" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G273" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H273" s="23" t="str">
-        <x:v>MHI/MSA</x:v>
+        <x:v>MKI</x:v>
       </x:c>
       <x:c r="I273" s="23" t="str">
         <x:v>404</x:v>
       </x:c>
       <x:c r="J273" s="23" t="str">
-        <x:v>MON P3</x:v>
-      </x:c>
-      <x:c r="K273" s="131" t="str"/>
-      <x:c r="L273" s="143" t="str"/>
-      <x:c r="M273" s="143" t="str"/>
-      <x:c r="N273" s="143" t="str"/>
-      <x:c r="O273" s="173" t="str"/>
+        <x:v>MON P4</x:v>
+      </x:c>
+      <x:c r="K273" s="131"/>
+      <x:c r="L273" s="143"/>
+      <x:c r="M273" s="143"/>
+      <x:c r="N273" s="143"/>
+      <x:c r="O273" s="173"/>
       <x:c r="P273" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A273)&gt;0,"No",IF(E273="BECM 3204",IF(J273='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E273="BECM 3208",IF(J273='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E273="CE 3224",IF(J273='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E273="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C273,2)=1,"Yes","No"),IF(MOD(C273,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13018,16 +13027,16 @@
         <x:v>MR</x:v>
       </x:c>
       <x:c r="I274" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J274" s="23" t="str">
         <x:v>MON P5</x:v>
       </x:c>
-      <x:c r="K274" s="131" t="str"/>
-      <x:c r="L274" s="143" t="str"/>
-      <x:c r="M274" s="143" t="str"/>
-      <x:c r="N274" s="143" t="str"/>
-      <x:c r="O274" s="173" t="str"/>
+      <x:c r="K274" s="131"/>
+      <x:c r="L274" s="143"/>
+      <x:c r="M274" s="143"/>
+      <x:c r="N274" s="143"/>
+      <x:c r="O274" s="173"/>
       <x:c r="P274" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A274)&gt;0,"No",IF(E274="BECM 3204",IF(J274='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E274="BECM 3208",IF(J274='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E274="CE 3224",IF(J274='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E274="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C274,2)=1,"Yes","No"),IF(MOD(C274,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13059,16 +13068,16 @@
         <x:v>AAM</x:v>
       </x:c>
       <x:c r="I275" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J275" s="23" t="str">
         <x:v>MON P6</x:v>
       </x:c>
-      <x:c r="K275" s="131" t="str"/>
-      <x:c r="L275" s="143" t="str"/>
-      <x:c r="M275" s="143" t="str"/>
-      <x:c r="N275" s="143" t="str"/>
-      <x:c r="O275" s="173" t="str"/>
+      <x:c r="K275" s="131"/>
+      <x:c r="L275" s="143"/>
+      <x:c r="M275" s="143"/>
+      <x:c r="N275" s="143"/>
+      <x:c r="O275" s="173"/>
       <x:c r="P275" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A275)&gt;0,"No",IF(E275="BECM 3204",IF(J275='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E275="BECM 3208",IF(J275='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E275="CE 3224",IF(J275='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E275="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C275,2)=1,"Yes","No"),IF(MOD(C275,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13088,26 +13097,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E276" s="23" t="str">
-        <x:v>BECM 3200</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F276" s="173" t="str">
-        <x:v>Project and Seminar</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G276" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H276" s="23" t="str">
-        <x:v>ALL</x:v>
-      </x:c>
-      <x:c r="I276" s="23" t="str"/>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I276" s="23"/>
       <x:c r="J276" s="23" t="str">
         <x:v>Mon PM</x:v>
       </x:c>
-      <x:c r="K276" s="131" t="str"/>
-      <x:c r="L276" s="143" t="str"/>
-      <x:c r="M276" s="143" t="str"/>
-      <x:c r="N276" s="143" t="str"/>
-      <x:c r="O276" s="173" t="str"/>
+      <x:c r="K276" s="131"/>
+      <x:c r="L276" s="143"/>
+      <x:c r="M276" s="143"/>
+      <x:c r="N276" s="143"/>
+      <x:c r="O276" s="173"/>
       <x:c r="P276" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A276)&gt;0,"No",IF(E276="BECM 3204",IF(J276='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E276="BECM 3208",IF(J276='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E276="CE 3224",IF(J276='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E276="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C276,2)=1,"Yes","No"),IF(MOD(C276,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13127,26 +13136,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E277" s="23" t="str">
-        <x:v>CE 3224</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F277" s="173" t="str">
-        <x:v>Sessional on Soil Mechanics</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G277" s="23" t="str">
-        <x:v>08:00 AM–10:30 AM</x:v>
+        <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H277" s="23" t="str">
-        <x:v>MHI/MRA</x:v>
-      </x:c>
-      <x:c r="I277" s="23" t="str"/>
+        <x:v>MKI</x:v>
+      </x:c>
+      <x:c r="I277" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J277" s="23" t="str">
-        <x:v>Tue AM</x:v>
-      </x:c>
-      <x:c r="K277" s="131" t="str"/>
-      <x:c r="L277" s="143" t="str"/>
-      <x:c r="M277" s="143" t="str"/>
-      <x:c r="N277" s="143" t="str"/>
-      <x:c r="O277" s="173" t="str"/>
+        <x:v>TUES P4</x:v>
+      </x:c>
+      <x:c r="K277" s="131"/>
+      <x:c r="L277" s="143"/>
+      <x:c r="M277" s="143"/>
+      <x:c r="N277" s="143"/>
+      <x:c r="O277" s="173"/>
       <x:c r="P277" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A277)&gt;0,"No",IF(E277="BECM 3204",IF(J277='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E277="BECM 3208",IF(J277='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E277="CE 3224",IF(J277='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E277="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C277,2)=1,"Yes","No"),IF(MOD(C277,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13166,28 +13177,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E278" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>CE 3211</x:v>
       </x:c>
       <x:c r="F278" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Structural Analysis and Design - II</x:v>
       </x:c>
       <x:c r="G278" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H278" s="23" t="str">
-        <x:v>MKI</x:v>
+        <x:v>ATB</x:v>
       </x:c>
       <x:c r="I278" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J278" s="23" t="str">
         <x:v>TUES P5</x:v>
       </x:c>
-      <x:c r="K278" s="131" t="str"/>
-      <x:c r="L278" s="143" t="str"/>
-      <x:c r="M278" s="143" t="str"/>
-      <x:c r="N278" s="143" t="str"/>
-      <x:c r="O278" s="173" t="str"/>
+      <x:c r="K278" s="131"/>
+      <x:c r="L278" s="143"/>
+      <x:c r="M278" s="143"/>
+      <x:c r="N278" s="143"/>
+      <x:c r="O278" s="173"/>
       <x:c r="P278" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A278)&gt;0,"No",IF(E278="BECM 3204",IF(J278='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E278="BECM 3208",IF(J278='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E278="CE 3224",IF(J278='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E278="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C278,2)=1,"Yes","No"),IF(MOD(C278,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13207,28 +13218,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E279" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F279" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G279" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H279" s="23" t="str">
-        <x:v>MRA</x:v>
+        <x:v>MSA</x:v>
       </x:c>
       <x:c r="I279" s="23" t="str">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J279" s="23" t="str">
         <x:v>TUES P6</x:v>
       </x:c>
-      <x:c r="K279" s="131" t="str"/>
-      <x:c r="L279" s="143" t="str"/>
-      <x:c r="M279" s="143" t="str"/>
-      <x:c r="N279" s="143" t="str"/>
-      <x:c r="O279" s="173" t="str"/>
+      <x:c r="K279" s="131"/>
+      <x:c r="L279" s="143"/>
+      <x:c r="M279" s="143"/>
+      <x:c r="N279" s="143"/>
+      <x:c r="O279" s="173"/>
       <x:c r="P279" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A279)&gt;0,"No",IF(E279="BECM 3204",IF(J279='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E279="BECM 3208",IF(J279='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E279="CE 3224",IF(J279='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E279="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C279,2)=1,"Yes","No"),IF(MOD(C279,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13248,26 +13259,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E280" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>CE 3224</x:v>
       </x:c>
       <x:c r="F280" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Sessional on Soil Mechanics</x:v>
       </x:c>
       <x:c r="G280" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H280" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I280" s="23" t="str"/>
+        <x:v>MHI/MRA</x:v>
+      </x:c>
+      <x:c r="I280" s="23"/>
       <x:c r="J280" s="23" t="str">
         <x:v>Tue PM</x:v>
       </x:c>
-      <x:c r="K280" s="131" t="str"/>
-      <x:c r="L280" s="143" t="str"/>
-      <x:c r="M280" s="143" t="str"/>
-      <x:c r="N280" s="143" t="str"/>
-      <x:c r="O280" s="173" t="str"/>
+      <x:c r="K280" s="131"/>
+      <x:c r="L280" s="143"/>
+      <x:c r="M280" s="143"/>
+      <x:c r="N280" s="143"/>
+      <x:c r="O280" s="173"/>
       <x:c r="P280" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A280)&gt;0,"No",IF(E280="BECM 3204",IF(J280='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E280="BECM 3208",IF(J280='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E280="CE 3224",IF(J280='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E280="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C280,2)=1,"Yes","No"),IF(MOD(C280,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13287,31 +13298,29 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E281" s="23" t="str">
-        <x:v>CE 3213</x:v>
+        <x:v>BECM 3208</x:v>
       </x:c>
       <x:c r="F281" s="173" t="str">
-        <x:v>Reinforced Concrete Structures - II</x:v>
+        <x:v>Landscape Design</x:v>
       </x:c>
       <x:c r="G281" s="23" t="str">
-        <x:v>09:40 AM–10:30 AM</x:v>
+        <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H281" s="23" t="str">
-        <x:v>HRS/MKI</x:v>
-      </x:c>
-      <x:c r="I281" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>MSH/MSA</x:v>
+      </x:c>
+      <x:c r="I281" s="23"/>
       <x:c r="J281" s="23" t="str">
-        <x:v>WED P3</x:v>
-      </x:c>
-      <x:c r="K281" s="131" t="str"/>
-      <x:c r="L281" s="143" t="str"/>
-      <x:c r="M281" s="143" t="str"/>
-      <x:c r="N281" s="143" t="str"/>
-      <x:c r="O281" s="173" t="str"/>
+        <x:v>Wed AM</x:v>
+      </x:c>
+      <x:c r="K281" s="131"/>
+      <x:c r="L281" s="143"/>
+      <x:c r="M281" s="143"/>
+      <x:c r="N281" s="143"/>
+      <x:c r="O281" s="173"/>
       <x:c r="P281" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A281)&gt;0,"No",IF(E281="BECM 3204",IF(J281='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E281="BECM 3208",IF(J281='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E281="CE 3224",IF(J281='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E281="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C281,2)=1,"Yes","No"),IF(MOD(C281,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -13328,28 +13337,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E282" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>CE 3223</x:v>
       </x:c>
       <x:c r="F282" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Soil Mechanics</x:v>
       </x:c>
       <x:c r="G282" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H282" s="23" t="str">
-        <x:v>ATB</x:v>
+        <x:v>MHI</x:v>
       </x:c>
       <x:c r="I282" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J282" s="23" t="str">
         <x:v>WED P4</x:v>
       </x:c>
-      <x:c r="K282" s="131" t="str"/>
-      <x:c r="L282" s="143" t="str"/>
-      <x:c r="M282" s="143" t="str"/>
-      <x:c r="N282" s="143" t="str"/>
-      <x:c r="O282" s="173" t="str"/>
+      <x:c r="K282" s="131"/>
+      <x:c r="L282" s="143"/>
+      <x:c r="M282" s="143"/>
+      <x:c r="N282" s="143"/>
+      <x:c r="O282" s="173"/>
       <x:c r="P282" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A282)&gt;0,"No",IF(E282="BECM 3204",IF(J282='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E282="BECM 3208",IF(J282='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E282="CE 3224",IF(J282='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E282="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C282,2)=1,"Yes","No"),IF(MOD(C282,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13369,28 +13378,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E283" s="23" t="str">
-        <x:v>CE 3223</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F283" s="173" t="str">
-        <x:v>Soil Mechanics</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G283" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H283" s="23" t="str">
-        <x:v>MHI</x:v>
+        <x:v>MR/MRA</x:v>
       </x:c>
       <x:c r="I283" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J283" s="23" t="str">
         <x:v>WED P5</x:v>
       </x:c>
-      <x:c r="K283" s="131" t="str"/>
-      <x:c r="L283" s="143" t="str"/>
-      <x:c r="M283" s="143" t="str"/>
-      <x:c r="N283" s="143" t="str"/>
-      <x:c r="O283" s="173" t="str"/>
+      <x:c r="K283" s="131"/>
+      <x:c r="L283" s="143"/>
+      <x:c r="M283" s="143"/>
+      <x:c r="N283" s="143"/>
+      <x:c r="O283" s="173"/>
       <x:c r="P283" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A283)&gt;0,"No",IF(E283="BECM 3204",IF(J283='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E283="BECM 3208",IF(J283='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E283="CE 3224",IF(J283='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E283="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C283,2)=1,"Yes","No"),IF(MOD(C283,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13422,16 +13431,16 @@
         <x:v>MSH/AAM</x:v>
       </x:c>
       <x:c r="I284" s="23" t="str">
-        <x:v>501</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J284" s="23" t="str">
         <x:v>WED P6</x:v>
       </x:c>
-      <x:c r="K284" s="131" t="str"/>
-      <x:c r="L284" s="143" t="str"/>
-      <x:c r="M284" s="143" t="str"/>
-      <x:c r="N284" s="143" t="str"/>
-      <x:c r="O284" s="173" t="str"/>
+      <x:c r="K284" s="131"/>
+      <x:c r="L284" s="143"/>
+      <x:c r="M284" s="143"/>
+      <x:c r="N284" s="143"/>
+      <x:c r="O284" s="173"/>
       <x:c r="P284" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A284)&gt;0,"No",IF(E284="BECM 3204",IF(J284='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E284="BECM 3208",IF(J284='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E284="CE 3224",IF(J284='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E284="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C284,2)=1,"Yes","No"),IF(MOD(C284,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13451,28 +13460,26 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E285" s="23" t="str">
-        <x:v>BECM 3208</x:v>
+        <x:v>BECM 3204</x:v>
       </x:c>
       <x:c r="F285" s="173" t="str">
-        <x:v>Landscape Design</x:v>
+        <x:v>Construction Techniques and Equipments - II</x:v>
       </x:c>
       <x:c r="G285" s="23" t="str">
         <x:v>02:30 PM–05:00 PM</x:v>
       </x:c>
       <x:c r="H285" s="23" t="str">
-        <x:v>MSH/MSA</x:v>
-      </x:c>
-      <x:c r="I285" s="23" t="str">
-        <x:v>501</x:v>
-      </x:c>
+        <x:v>HRS/MR</x:v>
+      </x:c>
+      <x:c r="I285" s="23"/>
       <x:c r="J285" s="23" t="str">
         <x:v>Wed PM</x:v>
       </x:c>
-      <x:c r="K285" s="131" t="str"/>
-      <x:c r="L285" s="143" t="str"/>
-      <x:c r="M285" s="143" t="str"/>
-      <x:c r="N285" s="143" t="str"/>
-      <x:c r="O285" s="173" t="str"/>
+      <x:c r="K285" s="131"/>
+      <x:c r="L285" s="143"/>
+      <x:c r="M285" s="143"/>
+      <x:c r="N285" s="143"/>
+      <x:c r="O285" s="173"/>
       <x:c r="P285" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A285)&gt;0,"No",IF(E285="BECM 3204",IF(J285='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E285="BECM 3208",IF(J285='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E285="CE 3224",IF(J285='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E285="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C285,2)=1,"Yes","No"),IF(MOD(C285,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -13492,29 +13499,31 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E286" s="23" t="str">
-        <x:v>BECM 3204</x:v>
+        <x:v>BECM 3200</x:v>
       </x:c>
       <x:c r="F286" s="173" t="str">
-        <x:v>Construction Techniques and Equipments - II</x:v>
+        <x:v>Project and Seminar</x:v>
       </x:c>
       <x:c r="G286" s="23" t="str">
         <x:v>08:00 AM–10:30 AM</x:v>
       </x:c>
       <x:c r="H286" s="23" t="str">
-        <x:v>HRS/MR</x:v>
-      </x:c>
-      <x:c r="I286" s="23" t="str"/>
+        <x:v>ALL</x:v>
+      </x:c>
+      <x:c r="I286" s="23" t="str">
+        <x:v>404</x:v>
+      </x:c>
       <x:c r="J286" s="23" t="str">
         <x:v>Thu AM</x:v>
       </x:c>
-      <x:c r="K286" s="131" t="str"/>
-      <x:c r="L286" s="143" t="str"/>
-      <x:c r="M286" s="143" t="str"/>
-      <x:c r="N286" s="143" t="str"/>
-      <x:c r="O286" s="173" t="str"/>
+      <x:c r="K286" s="131"/>
+      <x:c r="L286" s="143"/>
+      <x:c r="M286" s="143"/>
+      <x:c r="N286" s="143"/>
+      <x:c r="O286" s="173"/>
       <x:c r="P286" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A286)&gt;0,"No",IF(E286="BECM 3204",IF(J286='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E286="BECM 3208",IF(J286='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E286="CE 3224",IF(J286='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E286="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C286,2)=1,"Yes","No"),IF(MOD(C286,2)=0,"Yes","No")),"Yes")))))</x:f>
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -13531,28 +13540,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E287" s="23" t="str">
-        <x:v>BECM 3205</x:v>
+        <x:v>CE 3213</x:v>
       </x:c>
       <x:c r="F287" s="173" t="str">
-        <x:v>Acoustics and Lighting</x:v>
+        <x:v>Reinforced Concrete Structures - II</x:v>
       </x:c>
       <x:c r="G287" s="23" t="str">
         <x:v>10:40 AM–11:30 AM</x:v>
       </x:c>
       <x:c r="H287" s="23" t="str">
-        <x:v>MSH</x:v>
+        <x:v>HRS/MKI</x:v>
       </x:c>
       <x:c r="I287" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J287" s="23" t="str">
         <x:v>THURS P4</x:v>
       </x:c>
-      <x:c r="K287" s="131" t="str"/>
-      <x:c r="L287" s="143" t="str"/>
-      <x:c r="M287" s="143" t="str"/>
-      <x:c r="N287" s="143" t="str"/>
-      <x:c r="O287" s="173" t="str"/>
+      <x:c r="K287" s="131"/>
+      <x:c r="L287" s="143"/>
+      <x:c r="M287" s="143"/>
+      <x:c r="N287" s="143"/>
+      <x:c r="O287" s="173"/>
       <x:c r="P287" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A287)&gt;0,"No",IF(E287="BECM 3204",IF(J287='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E287="BECM 3208",IF(J287='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E287="CE 3224",IF(J287='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E287="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C287,2)=1,"Yes","No"),IF(MOD(C287,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13572,28 +13581,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E288" s="23" t="str">
-        <x:v>CE 3211</x:v>
+        <x:v>BECM 3201</x:v>
       </x:c>
       <x:c r="F288" s="173" t="str">
-        <x:v>Structural Analysis and Design - II</x:v>
+        <x:v>Construction and Project Management - II</x:v>
       </x:c>
       <x:c r="G288" s="23" t="str">
         <x:v>11:30 AM–12:20 PM</x:v>
       </x:c>
       <x:c r="H288" s="23" t="str">
-        <x:v>MKI/ATB</x:v>
+        <x:v>MRA</x:v>
       </x:c>
       <x:c r="I288" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J288" s="23" t="str">
         <x:v>THURS P5</x:v>
       </x:c>
-      <x:c r="K288" s="131" t="str"/>
-      <x:c r="L288" s="143" t="str"/>
-      <x:c r="M288" s="143" t="str"/>
-      <x:c r="N288" s="143" t="str"/>
-      <x:c r="O288" s="173" t="str"/>
+      <x:c r="K288" s="131"/>
+      <x:c r="L288" s="143"/>
+      <x:c r="M288" s="143"/>
+      <x:c r="N288" s="143"/>
+      <x:c r="O288" s="173"/>
       <x:c r="P288" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A288)&gt;0,"No",IF(E288="BECM 3204",IF(J288='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E288="BECM 3208",IF(J288='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E288="CE 3224",IF(J288='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E288="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C288,2)=1,"Yes","No"),IF(MOD(C288,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13613,28 +13622,28 @@
         <x:v>Regular</x:v>
       </x:c>
       <x:c r="E289" s="23" t="str">
-        <x:v>BECM 3201</x:v>
+        <x:v>BECM 3205</x:v>
       </x:c>
       <x:c r="F289" s="173" t="str">
-        <x:v>Construction and Project Management - II</x:v>
+        <x:v>Acoustics and Lighting</x:v>
       </x:c>
       <x:c r="G289" s="23" t="str">
         <x:v>12:20 PM–01:10 PM</x:v>
       </x:c>
       <x:c r="H289" s="23" t="str">
-        <x:v>MR/MRA</x:v>
+        <x:v>MSH</x:v>
       </x:c>
       <x:c r="I289" s="23" t="str">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="J289" s="23" t="str">
         <x:v>THURS P6</x:v>
       </x:c>
-      <x:c r="K289" s="131" t="str"/>
-      <x:c r="L289" s="143" t="str"/>
-      <x:c r="M289" s="143" t="str"/>
-      <x:c r="N289" s="143" t="str"/>
-      <x:c r="O289" s="173" t="str"/>
+      <x:c r="K289" s="131"/>
+      <x:c r="L289" s="143"/>
+      <x:c r="M289" s="143"/>
+      <x:c r="N289" s="143"/>
+      <x:c r="O289" s="173"/>
       <x:c r="P289" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A289)&gt;0,"No",IF(E289="BECM 3204",IF(J289='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E289="BECM 3208",IF(J289='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E289="CE 3224",IF(J289='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E289="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C289,2)=1,"Yes","No"),IF(MOD(C289,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>Yes</x:v>
@@ -13665,17 +13674,15 @@
       <x:c r="H290" s="23" t="str">
         <x:v>MHI/MRA</x:v>
       </x:c>
-      <x:c r="I290" s="23" t="str">
-        <x:v>405</x:v>
-      </x:c>
+      <x:c r="I290" s="23"/>
       <x:c r="J290" s="23" t="str">
         <x:v>Thu PM</x:v>
       </x:c>
-      <x:c r="K290" s="131" t="str"/>
-      <x:c r="L290" s="143" t="str"/>
-      <x:c r="M290" s="143" t="str"/>
-      <x:c r="N290" s="143" t="str"/>
-      <x:c r="O290" s="173" t="str"/>
+      <x:c r="K290" s="131"/>
+      <x:c r="L290" s="143"/>
+      <x:c r="M290" s="143"/>
+      <x:c r="N290" s="143"/>
+      <x:c r="O290" s="173"/>
       <x:c r="P290" s="159" t="str">
         <x:f>IF(COUNTIF('Routine &amp; Settings'!$I$5:$I$30,A290)&gt;0,"No",IF(E290="BECM 3204",IF(J290='Routine &amp; Settings'!$B$5,"Yes","No"),IF(E290="BECM 3208",IF(J290='Routine &amp; Settings'!$B$6,"Yes","No"),IF(E290="CE 3224",IF(J290='Routine &amp; Settings'!$B$7,"Yes","No"),IF(E290="BECM 3200",IF('Routine &amp; Settings'!$B$8="Odd Weeks",IF(MOD(C290,2)=1,"Yes","No"),IF(MOD(C290,2)=0,"Yes","No")),"Yes")))))</x:f>
         <x:v>No</x:v>
@@ -14491,7 +14498,7 @@
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Set your sessional slots once. The Class Log automatically ignores the alternate slot and the Puja break.</x:v>
+        <x:v>Official routine revised effective Sunday, 27 Sep 2026 (Week 4). Weeks 1–3 remain unchanged; Class Log uses the revised routine from Week 4 onward.</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -14537,7 +14544,7 @@
         <x:v>Sun PM</x:v>
       </x:c>
       <x:c r="C5" s="23" t="str">
-        <x:v>Sun PM or Thu AM</x:v>
+        <x:v>Sun PM or Wed PM</x:v>
       </x:c>
       <x:c r="E5" s="37" t="n">
         <x:v>1</x:v>
@@ -14560,10 +14567,10 @@
         <x:v>BECM 3208 slot</x:v>
       </x:c>
       <x:c r="B6" s="27" t="str">
-        <x:v>Tue PM</x:v>
+        <x:v>Mon PM</x:v>
       </x:c>
       <x:c r="C6" s="23" t="str">
-        <x:v>Tue PM or Wed PM</x:v>
+        <x:v>Mon PM or Wed AM</x:v>
       </x:c>
       <x:c r="E6" s="37" t="n">
         <x:v>2</x:v>
@@ -14586,10 +14593,10 @@
         <x:v>CE 3224 slot</x:v>
       </x:c>
       <x:c r="B7" s="27" t="str">
-        <x:v>Tue AM</x:v>
+        <x:v>Tue PM</x:v>
       </x:c>
       <x:c r="C7" s="23" t="str">
-        <x:v>Tue AM or Thu PM</x:v>
+        <x:v>Tue PM or Thu PM</x:v>
       </x:c>
       <x:c r="E7" s="37" t="n">
         <x:v>3</x:v>
@@ -14703,41 +14710,41 @@
       <x:c r="A12" s="92" t="str">
         <x:v>SUN</x:v>
       </x:c>
-      <x:c r="B12" s="76" t="str"/>
-      <x:c r="C12" s="76" t="str"/>
-      <x:c r="D12" s="76" t="str"/>
+      <x:c r="B12" s="76"/>
+      <x:c r="C12" s="76"/>
+      <x:c r="D12" s="76"/>
       <x:c r="E12" s="76" t="str">
         <x:v>CE 3213
 HRS</x:v>
       </x:c>
       <x:c r="F12" s="77" t="str">
+        <x:v>CE 3211
+MKI/ATB</x:v>
+      </x:c>
+      <x:c r="G12" s="77" t="str">
         <x:v>CE 3223
-MSA</x:v>
-      </x:c>
-      <x:c r="G12" s="77" t="str">
-        <x:v>CE 3211
-MKI</x:v>
+MHI/MSA</x:v>
       </x:c>
       <x:c r="H12" s="76" t="str">
         <x:v>BECM 3204
 Sun PM</x:v>
       </x:c>
-      <x:c r="I12" s="78" t="str"/>
+      <x:c r="I12" s="78"/>
       <x:c r="J12" s="79" t="str">
-        <x:v>Rm 404 / 501</x:v>
+        <x:v>Theory: Rm 404</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="50" customHeight="1">
       <x:c r="A13" s="92" t="str">
         <x:v>MON</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="str"/>
-      <x:c r="C13" s="76" t="str"/>
-      <x:c r="D13" s="76" t="str">
-        <x:v>CE 3223
-MHI/MSA</x:v>
-      </x:c>
-      <x:c r="E13" s="76" t="str"/>
+      <x:c r="B13" s="76"/>
+      <x:c r="C13" s="76"/>
+      <x:c r="D13" s="76"/>
+      <x:c r="E13" s="76" t="str">
+        <x:v>CE 3211
+MKI</x:v>
+      </x:c>
       <x:c r="F13" s="77" t="str">
         <x:v>BECM 3201
 MR</x:v>
@@ -14747,116 +14754,117 @@
 AAM</x:v>
       </x:c>
       <x:c r="H13" s="76" t="str">
-        <x:v>BECM 3200
+        <x:v>BECM 3208
 Mon PM</x:v>
       </x:c>
-      <x:c r="I13" s="78" t="str"/>
+      <x:c r="I13" s="78"/>
       <x:c r="J13" s="79" t="str">
-        <x:v>Rm 404 / 405</x:v>
+        <x:v>Theory: Rm 404</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="50" customHeight="1">
       <x:c r="A14" s="92" t="str">
         <x:v>TUES</x:v>
       </x:c>
-      <x:c r="B14" s="76" t="str">
-        <x:v>CE 3224
-Tue AM</x:v>
-      </x:c>
-      <x:c r="C14" s="76" t="str"/>
-      <x:c r="D14" s="76" t="str"/>
-      <x:c r="E14" s="76" t="str"/>
-      <x:c r="F14" s="77" t="str">
+      <x:c r="B14" s="76"/>
+      <x:c r="C14" s="76"/>
+      <x:c r="D14" s="76"/>
+      <x:c r="E14" s="76" t="str">
         <x:v>CE 3213
 MKI</x:v>
       </x:c>
+      <x:c r="F14" s="77" t="str">
+        <x:v>CE 3211
+ATB</x:v>
+      </x:c>
       <x:c r="G14" s="77" t="str">
-        <x:v>BECM 3201
-MRA</x:v>
+        <x:v>CE 3223
+MSA</x:v>
       </x:c>
       <x:c r="H14" s="76" t="str">
-        <x:v>BECM 3208
+        <x:v>CE 3224
 Tue PM</x:v>
       </x:c>
-      <x:c r="I14" s="78" t="str"/>
+      <x:c r="I14" s="78"/>
       <x:c r="J14" s="79" t="str">
-        <x:v>Rm 405</x:v>
+        <x:v>Theory: Rm 404</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="50" customHeight="1">
       <x:c r="A15" s="92" t="str">
         <x:v>WED</x:v>
       </x:c>
-      <x:c r="B15" s="76" t="str"/>
-      <x:c r="C15" s="76" t="str"/>
-      <x:c r="D15" s="76" t="str">
-        <x:v>CE 3213
-HRS/MKI</x:v>
-      </x:c>
+      <x:c r="B15" s="76" t="str">
+        <x:v>BECM 3208
+Wed AM</x:v>
+      </x:c>
+      <x:c r="C15" s="76"/>
+      <x:c r="D15" s="76"/>
       <x:c r="E15" s="76" t="str">
-        <x:v>CE 3211
-ATB</x:v>
-      </x:c>
-      <x:c r="F15" s="77" t="str">
         <x:v>CE 3223
 MHI</x:v>
+      </x:c>
+      <x:c r="F15" s="77" t="str">
+        <x:v>BECM 3201
+MR/MRA</x:v>
       </x:c>
       <x:c r="G15" s="77" t="str">
         <x:v>BECM 3205
 MSH/AAM</x:v>
       </x:c>
       <x:c r="H15" s="76" t="str">
-        <x:v>BECM 3208
+        <x:v>BECM 3204
 Wed PM</x:v>
       </x:c>
-      <x:c r="I15" s="78" t="str"/>
+      <x:c r="I15" s="78"/>
       <x:c r="J15" s="79" t="str">
-        <x:v>Rm 501</x:v>
+        <x:v>Theory: Rm 404</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="50" customHeight="1">
       <x:c r="A16" s="92" t="str">
-        <x:v>THU</x:v>
+        <x:v>THURS</x:v>
       </x:c>
       <x:c r="B16" s="76" t="str">
-        <x:v>BECM 3204
+        <x:v>BECM 3200
 Thu AM</x:v>
       </x:c>
-      <x:c r="C16" s="76" t="str"/>
-      <x:c r="D16" s="76" t="str"/>
+      <x:c r="C16" s="76"/>
+      <x:c r="D16" s="76"/>
       <x:c r="E16" s="76" t="str">
+        <x:v>CE 3213
+HRS/MKI</x:v>
+      </x:c>
+      <x:c r="F16" s="77" t="str">
+        <x:v>BECM 3201
+MRA</x:v>
+      </x:c>
+      <x:c r="G16" s="77" t="str">
         <x:v>BECM 3205
 MSH</x:v>
-      </x:c>
-      <x:c r="F16" s="77" t="str">
-        <x:v>CE 3211
-MKI/ATB</x:v>
-      </x:c>
-      <x:c r="G16" s="77" t="str">
-        <x:v>BECM 3201
-MR/MRA</x:v>
       </x:c>
       <x:c r="H16" s="76" t="str">
         <x:v>CE 3224
 Thu PM</x:v>
       </x:c>
-      <x:c r="I16" s="78" t="str"/>
+      <x:c r="I16" s="78"/>
       <x:c r="J16" s="79" t="str">
-        <x:v>Rm 405 / 406</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="E17" s="37" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F17" s="38" t="n">
-        <x:v>46362</x:v>
-      </x:c>
-      <x:c r="G17" s="38" t="n">
-        <x:v>46366</x:v>
-      </x:c>
-      <x:c r="I17" s="47"/>
-      <x:c r="J17" s="48"/>
+        <x:v>Theory: Rm 404</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="219" t="str">
+        <x:v>Revised routine effective from Sunday, 27 September 2026 • New Academic Building (B-Block, 3rd Floor) • Theory room: 404</x:v>
+      </x:c>
+      <x:c r="B17" s="219"/>
+      <x:c r="C17" s="219"/>
+      <x:c r="D17" s="219"/>
+      <x:c r="E17" s="219"/>
+      <x:c r="F17" s="220"/>
+      <x:c r="G17" s="220"/>
+      <x:c r="H17" s="219"/>
+      <x:c r="I17" s="220"/>
+      <x:c r="J17" s="219"/>
     </x:row>
     <x:row r="18">
       <x:c r="I18" s="47"/>
@@ -15031,16 +15039,17 @@
     <x:mergeCell ref="A2:J2"/>
     <x:mergeCell ref="A19:G19"/>
     <x:mergeCell ref="A28:J28"/>
+    <x:mergeCell ref="A17:J17"/>
   </x:mergeCells>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="B5">
-      <x:formula1>"Sun PM,Thu AM"</x:formula1>
+      <x:formula1>"Sun PM,Wed PM"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B6">
-      <x:formula1>"Tue PM,Wed PM"</x:formula1>
+      <x:formula1>"Mon PM,Wed AM"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B7">
-      <x:formula1>"Tue AM,Thu PM"</x:formula1>
+      <x:formula1>"Tue PM,Thu PM"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B8">
       <x:formula1>"Odd Weeks,Even Weeks"</x:formula1>
